--- a/feature/ui/src/androidMain/assets/reporte_mensual.xlsx
+++ b/feature/ui/src/androidMain/assets/reporte_mensual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelpanduro/Documents/Projects/LosJardinesKMP/feature/ui/src/androidMain/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2555F4-9759-9648-8DFA-1495533788B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB2150E-6670-0B4F-B1EB-0D60545D34DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{DBCE0E2E-2AEC-BE47-A25B-21C087ED2F3E}"/>
   </bookViews>
@@ -1994,6 +1994,381 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="54" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="47" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="11" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="11" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="15" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="11" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="11" borderId="12" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="29" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="28" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="21" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="44" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="16" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="7" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2006,10 +2381,358 @@
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="40" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="12" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="16" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="7" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="12" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2024,9 +2747,6 @@
     <xf numFmtId="3" fontId="3" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2043,15 +2763,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2071,717 +2782,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="7" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="5" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="12" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="16" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="16" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="12" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="11" borderId="13" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="11" borderId="12" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="43" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="40" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="21" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="44" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="15" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="29" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="28" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="11" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="11" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="47" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="9" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="39" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="8" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="8" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="8" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="54" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="44" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="8" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="8" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="47" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="47" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3404,80 +3404,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="316" t="s">
+      <c r="A1" s="130" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="316"/>
-      <c r="C1" s="316"/>
-      <c r="D1" s="316"/>
-      <c r="E1" s="316"/>
-      <c r="F1" s="316"/>
-      <c r="G1" s="316"/>
-      <c r="H1" s="316"/>
-      <c r="I1" s="316"/>
-      <c r="J1" s="316"/>
-      <c r="K1" s="316"/>
-      <c r="L1" s="316"/>
-      <c r="M1" s="316"/>
-      <c r="N1" s="316"/>
-      <c r="O1" s="316"/>
-      <c r="P1" s="316"/>
-      <c r="Q1" s="316"/>
-      <c r="R1" s="316"/>
-      <c r="S1" s="316"/>
-      <c r="T1" s="316"/>
-      <c r="U1" s="316"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
+      <c r="I1" s="130"/>
+      <c r="J1" s="130"/>
+      <c r="K1" s="130"/>
+      <c r="L1" s="130"/>
+      <c r="M1" s="130"/>
+      <c r="N1" s="130"/>
+      <c r="O1" s="130"/>
+      <c r="P1" s="130"/>
+      <c r="Q1" s="130"/>
+      <c r="R1" s="130"/>
+      <c r="S1" s="130"/>
+      <c r="T1" s="130"/>
+      <c r="U1" s="130"/>
     </row>
     <row r="2" spans="1:21" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="317" t="s">
+      <c r="A2" s="131" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="317"/>
-      <c r="C2" s="317"/>
-      <c r="D2" s="317"/>
-      <c r="E2" s="317"/>
-      <c r="F2" s="317"/>
-      <c r="G2" s="317"/>
-      <c r="H2" s="317"/>
-      <c r="I2" s="317"/>
-      <c r="J2" s="317"/>
-      <c r="K2" s="317"/>
-      <c r="L2" s="317"/>
-      <c r="M2" s="317"/>
-      <c r="N2" s="317"/>
-      <c r="O2" s="317"/>
-      <c r="P2" s="317"/>
-      <c r="Q2" s="317"/>
-      <c r="R2" s="317"/>
-      <c r="S2" s="317"/>
-      <c r="T2" s="317"/>
-      <c r="U2" s="317"/>
+      <c r="B2" s="131"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="131"/>
+      <c r="N2" s="131"/>
+      <c r="O2" s="131"/>
+      <c r="P2" s="131"/>
+      <c r="Q2" s="131"/>
+      <c r="R2" s="131"/>
+      <c r="S2" s="131"/>
+      <c r="T2" s="131"/>
+      <c r="U2" s="131"/>
     </row>
     <row r="3" spans="1:21" ht="10" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:21" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="318" t="s">
+      <c r="A4" s="132" t="s">
         <v>199</v>
       </c>
-      <c r="B4" s="319"/>
-      <c r="C4" s="319"/>
-      <c r="D4" s="319"/>
-      <c r="E4" s="319"/>
-      <c r="F4" s="319"/>
-      <c r="G4" s="319"/>
-      <c r="H4" s="319"/>
-      <c r="I4" s="319"/>
-      <c r="J4" s="319"/>
-      <c r="K4" s="319"/>
-      <c r="L4" s="319"/>
-      <c r="M4" s="319"/>
-      <c r="N4" s="319"/>
-      <c r="O4" s="319"/>
-      <c r="P4" s="319"/>
-      <c r="Q4" s="319"/>
-      <c r="R4" s="319"/>
-      <c r="S4" s="319"/>
-      <c r="T4" s="319"/>
-      <c r="U4" s="320"/>
+      <c r="B4" s="133"/>
+      <c r="C4" s="133"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="133"/>
+      <c r="K4" s="133"/>
+      <c r="L4" s="133"/>
+      <c r="M4" s="133"/>
+      <c r="N4" s="133"/>
+      <c r="O4" s="133"/>
+      <c r="P4" s="133"/>
+      <c r="Q4" s="133"/>
+      <c r="R4" s="133"/>
+      <c r="S4" s="133"/>
+      <c r="T4" s="133"/>
+      <c r="U4" s="134"/>
     </row>
     <row r="5" spans="1:21" ht="5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="89"/>
@@ -3503,29 +3503,29 @@
       <c r="U5" s="89"/>
     </row>
     <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="321" t="s">
+      <c r="A6" s="135" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="321"/>
-      <c r="C6" s="321"/>
-      <c r="D6" s="321"/>
-      <c r="E6" s="321"/>
-      <c r="F6" s="321"/>
-      <c r="G6" s="321"/>
-      <c r="H6" s="321"/>
-      <c r="I6" s="321"/>
-      <c r="J6" s="321"/>
-      <c r="K6" s="321"/>
-      <c r="L6" s="321"/>
-      <c r="M6" s="321"/>
-      <c r="N6" s="321"/>
-      <c r="O6" s="321"/>
-      <c r="P6" s="321"/>
-      <c r="Q6" s="321"/>
-      <c r="R6" s="321"/>
-      <c r="S6" s="321"/>
-      <c r="T6" s="321"/>
-      <c r="U6" s="321"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="135"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="135"/>
+      <c r="M6" s="135"/>
+      <c r="N6" s="135"/>
+      <c r="O6" s="135"/>
+      <c r="P6" s="135"/>
+      <c r="Q6" s="135"/>
+      <c r="R6" s="135"/>
+      <c r="S6" s="135"/>
+      <c r="T6" s="135"/>
+      <c r="U6" s="135"/>
     </row>
     <row r="7" spans="1:21" ht="10" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="88"/>
@@ -3546,29 +3546,29 @@
       <c r="P7" s="88"/>
     </row>
     <row r="8" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="322" t="s">
+      <c r="A8" s="105" t="s">
         <v>197</v>
       </c>
-      <c r="B8" s="323"/>
-      <c r="C8" s="323"/>
-      <c r="D8" s="323"/>
-      <c r="E8" s="323"/>
-      <c r="F8" s="323"/>
-      <c r="G8" s="323"/>
-      <c r="H8" s="323"/>
-      <c r="I8" s="323"/>
-      <c r="J8" s="323"/>
-      <c r="K8" s="323"/>
-      <c r="L8" s="323"/>
-      <c r="M8" s="323"/>
-      <c r="N8" s="323"/>
-      <c r="O8" s="323"/>
-      <c r="P8" s="323"/>
-      <c r="Q8" s="323"/>
-      <c r="R8" s="323"/>
-      <c r="S8" s="323"/>
-      <c r="T8" s="323"/>
-      <c r="U8" s="324"/>
+      <c r="B8" s="106"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="106"/>
+      <c r="F8" s="106"/>
+      <c r="G8" s="106"/>
+      <c r="H8" s="106"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="106"/>
+      <c r="K8" s="106"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="106"/>
+      <c r="N8" s="106"/>
+      <c r="O8" s="106"/>
+      <c r="P8" s="106"/>
+      <c r="Q8" s="106"/>
+      <c r="R8" s="106"/>
+      <c r="S8" s="106"/>
+      <c r="T8" s="106"/>
+      <c r="U8" s="107"/>
     </row>
     <row r="9" spans="1:21" ht="5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="70"/>
@@ -3588,300 +3588,300 @@
       <c r="U9" s="23"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="279" t="s">
+      <c r="A10" s="136" t="s">
         <v>196</v>
       </c>
-      <c r="B10" s="280"/>
-      <c r="C10" s="281" t="s">
+      <c r="B10" s="137"/>
+      <c r="C10" s="138" t="s">
         <v>177</v>
       </c>
-      <c r="D10" s="281"/>
-      <c r="E10" s="281"/>
-      <c r="F10" s="281"/>
-      <c r="G10" s="281"/>
-      <c r="H10" s="282" t="s">
+      <c r="D10" s="138"/>
+      <c r="E10" s="138"/>
+      <c r="F10" s="138"/>
+      <c r="G10" s="138"/>
+      <c r="H10" s="139" t="s">
         <v>195</v>
       </c>
-      <c r="I10" s="282"/>
-      <c r="J10" s="281">
+      <c r="I10" s="139"/>
+      <c r="J10" s="138">
         <v>10009519195</v>
       </c>
-      <c r="K10" s="281"/>
-      <c r="L10" s="281"/>
-      <c r="M10" s="281"/>
-      <c r="N10" s="282" t="s">
+      <c r="K10" s="138"/>
+      <c r="L10" s="138"/>
+      <c r="M10" s="138"/>
+      <c r="N10" s="139" t="s">
         <v>194</v>
       </c>
-      <c r="O10" s="282"/>
-      <c r="P10" s="325"/>
-      <c r="Q10" s="325"/>
-      <c r="R10" s="282" t="s">
+      <c r="O10" s="139"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="139" t="s">
         <v>193</v>
       </c>
-      <c r="S10" s="282"/>
-      <c r="T10" s="326"/>
-      <c r="U10" s="327"/>
+      <c r="S10" s="139"/>
+      <c r="T10" s="141"/>
+      <c r="U10" s="142"/>
     </row>
     <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="279" t="s">
+      <c r="A11" s="136" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="280"/>
-      <c r="C11" s="281" t="s">
+      <c r="B11" s="137"/>
+      <c r="C11" s="138" t="s">
         <v>191</v>
       </c>
-      <c r="D11" s="281"/>
-      <c r="E11" s="281"/>
-      <c r="F11" s="281"/>
-      <c r="G11" s="281"/>
-      <c r="H11" s="281"/>
-      <c r="I11" s="281"/>
-      <c r="J11" s="281"/>
-      <c r="K11" s="281"/>
-      <c r="L11" s="281"/>
-      <c r="M11" s="281"/>
-      <c r="N11" s="281"/>
-      <c r="O11" s="281"/>
-      <c r="P11" s="281"/>
-      <c r="Q11" s="281"/>
-      <c r="R11" s="282" t="s">
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="138"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="138"/>
+      <c r="J11" s="138"/>
+      <c r="K11" s="138"/>
+      <c r="L11" s="138"/>
+      <c r="M11" s="138"/>
+      <c r="N11" s="138"/>
+      <c r="O11" s="138"/>
+      <c r="P11" s="138"/>
+      <c r="Q11" s="138"/>
+      <c r="R11" s="139" t="s">
         <v>190</v>
       </c>
-      <c r="S11" s="282"/>
-      <c r="T11" s="311"/>
-      <c r="U11" s="312"/>
+      <c r="S11" s="139"/>
+      <c r="T11" s="143"/>
+      <c r="U11" s="144"/>
     </row>
     <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="279" t="s">
+      <c r="A12" s="136" t="s">
         <v>189</v>
       </c>
-      <c r="B12" s="280"/>
-      <c r="C12" s="313" t="s">
+      <c r="B12" s="137"/>
+      <c r="C12" s="145" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="313"/>
-      <c r="E12" s="313"/>
-      <c r="F12" s="313"/>
-      <c r="G12" s="313"/>
-      <c r="H12" s="313"/>
-      <c r="I12" s="313"/>
-      <c r="J12" s="313"/>
-      <c r="K12" s="313"/>
-      <c r="L12" s="313"/>
-      <c r="M12" s="313"/>
-      <c r="N12" s="313"/>
-      <c r="O12" s="313"/>
-      <c r="P12" s="313"/>
-      <c r="Q12" s="313"/>
-      <c r="R12" s="313"/>
-      <c r="S12" s="313"/>
-      <c r="T12" s="313"/>
-      <c r="U12" s="314"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="145"/>
+      <c r="K12" s="145"/>
+      <c r="L12" s="145"/>
+      <c r="M12" s="145"/>
+      <c r="N12" s="145"/>
+      <c r="O12" s="145"/>
+      <c r="P12" s="145"/>
+      <c r="Q12" s="145"/>
+      <c r="R12" s="145"/>
+      <c r="S12" s="145"/>
+      <c r="T12" s="145"/>
+      <c r="U12" s="146"/>
     </row>
     <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="279" t="s">
+      <c r="A13" s="136" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="280"/>
-      <c r="C13" s="281" t="s">
+      <c r="B13" s="137"/>
+      <c r="C13" s="138" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="281"/>
-      <c r="E13" s="281"/>
-      <c r="F13" s="282" t="s">
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="139" t="s">
         <v>185</v>
       </c>
-      <c r="G13" s="282"/>
-      <c r="H13" s="281" t="s">
+      <c r="G13" s="139"/>
+      <c r="H13" s="138" t="s">
         <v>183</v>
       </c>
-      <c r="I13" s="281"/>
-      <c r="J13" s="282" t="s">
+      <c r="I13" s="138"/>
+      <c r="J13" s="139" t="s">
         <v>184</v>
       </c>
-      <c r="K13" s="282"/>
-      <c r="L13" s="281" t="s">
+      <c r="K13" s="139"/>
+      <c r="L13" s="138" t="s">
         <v>183</v>
       </c>
-      <c r="M13" s="281"/>
-      <c r="N13" s="281"/>
-      <c r="O13" s="281"/>
-      <c r="P13" s="281"/>
-      <c r="Q13" s="281"/>
-      <c r="R13" s="281"/>
-      <c r="S13" s="281"/>
-      <c r="T13" s="281"/>
-      <c r="U13" s="315"/>
+      <c r="M13" s="138"/>
+      <c r="N13" s="138"/>
+      <c r="O13" s="138"/>
+      <c r="P13" s="138"/>
+      <c r="Q13" s="138"/>
+      <c r="R13" s="138"/>
+      <c r="S13" s="138"/>
+      <c r="T13" s="138"/>
+      <c r="U13" s="147"/>
     </row>
     <row r="14" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="279" t="s">
+      <c r="A14" s="136" t="s">
         <v>176</v>
       </c>
-      <c r="B14" s="280"/>
-      <c r="C14" s="281">
+      <c r="B14" s="137"/>
+      <c r="C14" s="138">
         <v>951638535</v>
       </c>
-      <c r="D14" s="281"/>
-      <c r="E14" s="281"/>
-      <c r="F14" s="281"/>
-      <c r="G14" s="281"/>
-      <c r="H14" s="281"/>
-      <c r="I14" s="281"/>
-      <c r="J14" s="281"/>
-      <c r="K14" s="281"/>
-      <c r="L14" s="281"/>
-      <c r="M14" s="281"/>
-      <c r="N14" s="282" t="s">
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="M14" s="138"/>
+      <c r="N14" s="139" t="s">
         <v>182</v>
       </c>
-      <c r="O14" s="282"/>
-      <c r="P14" s="282"/>
-      <c r="Q14" s="283"/>
-      <c r="R14" s="283"/>
-      <c r="S14" s="283"/>
-      <c r="T14" s="283"/>
-      <c r="U14" s="284"/>
+      <c r="O14" s="139"/>
+      <c r="P14" s="139"/>
+      <c r="Q14" s="159"/>
+      <c r="R14" s="159"/>
+      <c r="S14" s="159"/>
+      <c r="T14" s="159"/>
+      <c r="U14" s="160"/>
     </row>
     <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="279" t="s">
+      <c r="A15" s="136" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="280"/>
-      <c r="C15" s="285"/>
-      <c r="D15" s="285"/>
-      <c r="E15" s="285"/>
-      <c r="F15" s="285"/>
-      <c r="G15" s="285"/>
-      <c r="H15" s="285"/>
-      <c r="I15" s="285"/>
-      <c r="J15" s="285"/>
-      <c r="K15" s="285"/>
-      <c r="L15" s="285"/>
-      <c r="M15" s="285"/>
-      <c r="N15" s="282" t="s">
+      <c r="B15" s="137"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="148"/>
+      <c r="I15" s="148"/>
+      <c r="J15" s="148"/>
+      <c r="K15" s="148"/>
+      <c r="L15" s="148"/>
+      <c r="M15" s="148"/>
+      <c r="N15" s="139" t="s">
         <v>180</v>
       </c>
-      <c r="O15" s="282"/>
-      <c r="P15" s="282"/>
-      <c r="Q15" s="285" t="s">
+      <c r="O15" s="139"/>
+      <c r="P15" s="139"/>
+      <c r="Q15" s="148" t="s">
         <v>174</v>
       </c>
-      <c r="R15" s="285"/>
-      <c r="S15" s="285"/>
-      <c r="T15" s="285"/>
-      <c r="U15" s="301"/>
+      <c r="R15" s="148"/>
+      <c r="S15" s="148"/>
+      <c r="T15" s="148"/>
+      <c r="U15" s="149"/>
     </row>
     <row r="16" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="307" t="s">
+      <c r="A16" s="155" t="s">
         <v>179</v>
       </c>
-      <c r="B16" s="308"/>
-      <c r="C16" s="308"/>
-      <c r="D16" s="308"/>
-      <c r="E16" s="308"/>
-      <c r="F16" s="308"/>
-      <c r="G16" s="308"/>
-      <c r="H16" s="308"/>
-      <c r="I16" s="308"/>
-      <c r="J16" s="308"/>
-      <c r="K16" s="308"/>
-      <c r="L16" s="308"/>
-      <c r="M16" s="308"/>
-      <c r="N16" s="308"/>
-      <c r="O16" s="308"/>
-      <c r="P16" s="308"/>
-      <c r="Q16" s="308"/>
-      <c r="R16" s="308"/>
-      <c r="S16" s="308"/>
-      <c r="T16" s="308"/>
-      <c r="U16" s="309"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="156"/>
+      <c r="H16" s="156"/>
+      <c r="I16" s="156"/>
+      <c r="J16" s="156"/>
+      <c r="K16" s="156"/>
+      <c r="L16" s="156"/>
+      <c r="M16" s="156"/>
+      <c r="N16" s="156"/>
+      <c r="O16" s="156"/>
+      <c r="P16" s="156"/>
+      <c r="Q16" s="156"/>
+      <c r="R16" s="156"/>
+      <c r="S16" s="156"/>
+      <c r="T16" s="156"/>
+      <c r="U16" s="157"/>
     </row>
     <row r="17" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="330" t="s">
+      <c r="A17" s="102" t="s">
         <v>178</v>
       </c>
-      <c r="B17" s="331"/>
-      <c r="C17" s="332" t="s">
+      <c r="B17" s="103"/>
+      <c r="C17" s="104" t="s">
         <v>177</v>
       </c>
-      <c r="D17" s="332"/>
-      <c r="E17" s="332"/>
-      <c r="F17" s="332"/>
-      <c r="G17" s="332"/>
-      <c r="H17" s="332"/>
-      <c r="I17" s="332"/>
-      <c r="J17" s="282" t="s">
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="139" t="s">
         <v>176</v>
       </c>
-      <c r="K17" s="282"/>
-      <c r="L17" s="310">
+      <c r="K17" s="139"/>
+      <c r="L17" s="158">
         <v>951638535</v>
       </c>
-      <c r="M17" s="310"/>
-      <c r="N17" s="282" t="s">
+      <c r="M17" s="158"/>
+      <c r="N17" s="139" t="s">
         <v>175</v>
       </c>
-      <c r="O17" s="282"/>
-      <c r="P17" s="285" t="s">
+      <c r="O17" s="139"/>
+      <c r="P17" s="148" t="s">
         <v>174</v>
       </c>
-      <c r="Q17" s="285"/>
-      <c r="R17" s="285"/>
-      <c r="S17" s="285"/>
-      <c r="T17" s="285"/>
-      <c r="U17" s="301"/>
+      <c r="Q17" s="148"/>
+      <c r="R17" s="148"/>
+      <c r="S17" s="148"/>
+      <c r="T17" s="148"/>
+      <c r="U17" s="149"/>
     </row>
     <row r="18" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="307" t="s">
+      <c r="A18" s="155" t="s">
         <v>173</v>
       </c>
-      <c r="B18" s="308"/>
-      <c r="C18" s="308"/>
-      <c r="D18" s="308"/>
-      <c r="E18" s="308"/>
-      <c r="F18" s="308"/>
-      <c r="G18" s="308"/>
-      <c r="H18" s="308"/>
-      <c r="I18" s="308"/>
-      <c r="J18" s="308"/>
-      <c r="K18" s="308"/>
-      <c r="L18" s="308"/>
-      <c r="M18" s="308"/>
-      <c r="N18" s="308"/>
-      <c r="O18" s="308"/>
-      <c r="P18" s="308"/>
-      <c r="Q18" s="308"/>
-      <c r="R18" s="308"/>
-      <c r="S18" s="308"/>
-      <c r="T18" s="308"/>
-      <c r="U18" s="309"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="156"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="156"/>
+      <c r="H18" s="156"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="156"/>
+      <c r="K18" s="156"/>
+      <c r="L18" s="156"/>
+      <c r="M18" s="156"/>
+      <c r="N18" s="156"/>
+      <c r="O18" s="156"/>
+      <c r="P18" s="156"/>
+      <c r="Q18" s="156"/>
+      <c r="R18" s="156"/>
+      <c r="S18" s="156"/>
+      <c r="T18" s="156"/>
+      <c r="U18" s="157"/>
     </row>
     <row r="19" spans="1:23" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="302" t="s">
+      <c r="A19" s="150" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="303"/>
-      <c r="C19" s="304"/>
-      <c r="D19" s="304"/>
-      <c r="E19" s="304"/>
-      <c r="F19" s="304"/>
-      <c r="G19" s="304"/>
-      <c r="H19" s="304"/>
-      <c r="I19" s="304"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="152"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="152"/>
+      <c r="G19" s="152"/>
+      <c r="H19" s="152"/>
+      <c r="I19" s="152"/>
       <c r="J19" s="87" t="s">
         <v>171</v>
       </c>
       <c r="K19" s="86"/>
       <c r="L19" s="85"/>
-      <c r="M19" s="305"/>
-      <c r="N19" s="305"/>
-      <c r="O19" s="305"/>
-      <c r="P19" s="305"/>
-      <c r="Q19" s="305"/>
-      <c r="R19" s="305"/>
-      <c r="S19" s="305"/>
-      <c r="T19" s="305"/>
-      <c r="U19" s="306"/>
+      <c r="M19" s="153"/>
+      <c r="N19" s="153"/>
+      <c r="O19" s="153"/>
+      <c r="P19" s="153"/>
+      <c r="Q19" s="153"/>
+      <c r="R19" s="153"/>
+      <c r="S19" s="153"/>
+      <c r="T19" s="153"/>
+      <c r="U19" s="154"/>
     </row>
     <row r="20" spans="1:23" ht="10" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E20" s="84"/>
@@ -3897,27 +3897,27 @@
       <c r="P20" s="24"/>
     </row>
     <row r="21" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="322" t="s">
+      <c r="A21" s="105" t="s">
         <v>170</v>
       </c>
-      <c r="B21" s="323"/>
-      <c r="C21" s="323"/>
-      <c r="D21" s="323"/>
-      <c r="E21" s="323"/>
-      <c r="F21" s="323"/>
-      <c r="G21" s="323"/>
-      <c r="H21" s="323"/>
-      <c r="I21" s="323"/>
-      <c r="J21" s="323"/>
-      <c r="K21" s="323"/>
-      <c r="L21" s="323"/>
-      <c r="M21" s="323"/>
-      <c r="N21" s="323"/>
-      <c r="O21" s="323"/>
-      <c r="P21" s="323"/>
-      <c r="Q21" s="323"/>
-      <c r="R21" s="323"/>
-      <c r="S21" s="324"/>
+      <c r="B21" s="106"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="106"/>
+      <c r="J21" s="106"/>
+      <c r="K21" s="106"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="106"/>
+      <c r="N21" s="106"/>
+      <c r="O21" s="106"/>
+      <c r="P21" s="106"/>
+      <c r="Q21" s="106"/>
+      <c r="R21" s="106"/>
+      <c r="S21" s="107"/>
     </row>
     <row r="22" spans="1:23" ht="5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="70"/>
@@ -3937,266 +3937,266 @@
       <c r="S22" s="23"/>
     </row>
     <row r="23" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="333" t="s">
+      <c r="A23" s="108" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="334"/>
-      <c r="C23" s="335"/>
-      <c r="D23" s="339" t="s">
+      <c r="B23" s="109"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="340"/>
-      <c r="F23" s="340"/>
-      <c r="G23" s="340"/>
-      <c r="H23" s="340"/>
-      <c r="I23" s="341"/>
-      <c r="J23" s="339" t="s">
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="K23" s="340"/>
-      <c r="L23" s="340"/>
-      <c r="M23" s="340"/>
-      <c r="N23" s="340"/>
-      <c r="O23" s="341"/>
-      <c r="P23" s="290" t="s">
+      <c r="K23" s="115"/>
+      <c r="L23" s="115"/>
+      <c r="M23" s="115"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="116"/>
+      <c r="P23" s="120" t="s">
         <v>166</v>
       </c>
-      <c r="Q23" s="345"/>
-      <c r="R23" s="345"/>
-      <c r="S23" s="291"/>
+      <c r="Q23" s="121"/>
+      <c r="R23" s="121"/>
+      <c r="S23" s="122"/>
     </row>
     <row r="24" spans="1:23" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="333"/>
-      <c r="B24" s="334"/>
-      <c r="C24" s="335"/>
-      <c r="D24" s="342"/>
-      <c r="E24" s="343"/>
-      <c r="F24" s="343"/>
-      <c r="G24" s="343"/>
-      <c r="H24" s="343"/>
-      <c r="I24" s="344"/>
-      <c r="J24" s="342"/>
-      <c r="K24" s="343"/>
-      <c r="L24" s="343"/>
-      <c r="M24" s="343"/>
-      <c r="N24" s="343"/>
-      <c r="O24" s="344"/>
-      <c r="P24" s="290"/>
-      <c r="Q24" s="345"/>
-      <c r="R24" s="345"/>
-      <c r="S24" s="291"/>
+      <c r="A24" s="108"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="118"/>
+      <c r="N24" s="118"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="120"/>
+      <c r="Q24" s="121"/>
+      <c r="R24" s="121"/>
+      <c r="S24" s="122"/>
     </row>
     <row r="25" spans="1:23" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="333"/>
-      <c r="B25" s="334"/>
-      <c r="C25" s="335"/>
-      <c r="D25" s="288" t="s">
+      <c r="A25" s="108"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="123" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
-      <c r="G25" s="289"/>
-      <c r="H25" s="288" t="s">
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="123" t="s">
         <v>164</v>
       </c>
-      <c r="I25" s="289"/>
-      <c r="J25" s="288" t="s">
+      <c r="I25" s="125"/>
+      <c r="J25" s="123" t="s">
         <v>163</v>
       </c>
-      <c r="K25" s="289"/>
-      <c r="L25" s="288" t="s">
+      <c r="K25" s="125"/>
+      <c r="L25" s="123" t="s">
         <v>162</v>
       </c>
-      <c r="M25" s="289"/>
-      <c r="N25" s="288" t="s">
+      <c r="M25" s="125"/>
+      <c r="N25" s="123" t="s">
         <v>161</v>
       </c>
-      <c r="O25" s="289"/>
-      <c r="P25" s="290"/>
-      <c r="Q25" s="345"/>
-      <c r="R25" s="345"/>
-      <c r="S25" s="291"/>
+      <c r="O25" s="125"/>
+      <c r="P25" s="120"/>
+      <c r="Q25" s="121"/>
+      <c r="R25" s="121"/>
+      <c r="S25" s="122"/>
     </row>
     <row r="26" spans="1:23" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="333"/>
-      <c r="B26" s="334"/>
-      <c r="C26" s="335"/>
-      <c r="D26" s="292" t="s">
+      <c r="A26" s="108"/>
+      <c r="B26" s="109"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="161" t="s">
         <v>160</v>
       </c>
-      <c r="E26" s="293"/>
-      <c r="F26" s="292" t="s">
+      <c r="E26" s="162"/>
+      <c r="F26" s="161" t="s">
         <v>159</v>
       </c>
-      <c r="G26" s="293"/>
-      <c r="H26" s="290"/>
-      <c r="I26" s="291"/>
-      <c r="J26" s="290"/>
-      <c r="K26" s="291"/>
-      <c r="L26" s="290"/>
-      <c r="M26" s="291"/>
-      <c r="N26" s="290"/>
-      <c r="O26" s="291"/>
-      <c r="P26" s="292" t="s">
+      <c r="G26" s="162"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="122"/>
+      <c r="J26" s="120"/>
+      <c r="K26" s="122"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="122"/>
+      <c r="N26" s="120"/>
+      <c r="O26" s="122"/>
+      <c r="P26" s="161" t="s">
         <v>160</v>
       </c>
-      <c r="Q26" s="293"/>
-      <c r="R26" s="292" t="s">
+      <c r="Q26" s="162"/>
+      <c r="R26" s="161" t="s">
         <v>159</v>
       </c>
-      <c r="S26" s="293"/>
+      <c r="S26" s="162"/>
     </row>
     <row r="27" spans="1:23" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="336"/>
-      <c r="B27" s="337"/>
-      <c r="C27" s="338"/>
-      <c r="D27" s="286">
+      <c r="A27" s="111"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="100">
         <v>1</v>
       </c>
-      <c r="E27" s="287"/>
-      <c r="F27" s="286">
+      <c r="E27" s="101"/>
+      <c r="F27" s="100">
         <v>2</v>
       </c>
-      <c r="G27" s="287"/>
-      <c r="H27" s="286">
+      <c r="G27" s="101"/>
+      <c r="H27" s="100">
         <v>3</v>
       </c>
-      <c r="I27" s="287"/>
-      <c r="J27" s="286">
+      <c r="I27" s="101"/>
+      <c r="J27" s="100">
         <v>4</v>
       </c>
-      <c r="K27" s="287"/>
-      <c r="L27" s="286">
+      <c r="K27" s="101"/>
+      <c r="L27" s="100">
         <v>5</v>
       </c>
-      <c r="M27" s="287"/>
-      <c r="N27" s="286">
+      <c r="M27" s="101"/>
+      <c r="N27" s="100">
         <v>6</v>
       </c>
-      <c r="O27" s="287"/>
-      <c r="P27" s="286"/>
-      <c r="Q27" s="287"/>
-      <c r="R27" s="286"/>
-      <c r="S27" s="287"/>
+      <c r="O27" s="101"/>
+      <c r="P27" s="100"/>
+      <c r="Q27" s="101"/>
+      <c r="R27" s="100"/>
+      <c r="S27" s="101"/>
     </row>
     <row r="28" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="294" t="s">
+      <c r="A28" s="163" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="295"/>
-      <c r="C28" s="296"/>
-      <c r="D28" s="297"/>
-      <c r="E28" s="298"/>
-      <c r="F28" s="299"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="297"/>
-      <c r="I28" s="300"/>
-      <c r="J28" s="297"/>
-      <c r="K28" s="298"/>
-      <c r="L28" s="297"/>
-      <c r="M28" s="298"/>
-      <c r="N28" s="297"/>
-      <c r="O28" s="298"/>
-      <c r="P28" s="277"/>
-      <c r="Q28" s="278"/>
-      <c r="R28" s="277"/>
-      <c r="S28" s="278"/>
+      <c r="B28" s="164"/>
+      <c r="C28" s="165"/>
+      <c r="D28" s="126"/>
+      <c r="E28" s="127"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="167"/>
+      <c r="H28" s="126"/>
+      <c r="I28" s="168"/>
+      <c r="J28" s="126"/>
+      <c r="K28" s="127"/>
+      <c r="L28" s="126"/>
+      <c r="M28" s="127"/>
+      <c r="N28" s="126"/>
+      <c r="O28" s="127"/>
+      <c r="P28" s="128"/>
+      <c r="Q28" s="129"/>
+      <c r="R28" s="128"/>
+      <c r="S28" s="129"/>
       <c r="W28" s="83"/>
     </row>
     <row r="29" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="267" t="s">
+      <c r="A29" s="171" t="s">
         <v>157</v>
       </c>
-      <c r="B29" s="268"/>
-      <c r="C29" s="269"/>
-      <c r="D29" s="245"/>
-      <c r="E29" s="246"/>
-      <c r="F29" s="270"/>
-      <c r="G29" s="271"/>
-      <c r="H29" s="245"/>
-      <c r="I29" s="272"/>
-      <c r="J29" s="245"/>
-      <c r="K29" s="246"/>
-      <c r="L29" s="245"/>
-      <c r="M29" s="246"/>
-      <c r="N29" s="245"/>
-      <c r="O29" s="246"/>
-      <c r="P29" s="247"/>
-      <c r="Q29" s="248"/>
-      <c r="R29" s="247"/>
-      <c r="S29" s="248"/>
+      <c r="B29" s="172"/>
+      <c r="C29" s="173"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="175"/>
+      <c r="F29" s="181"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="174"/>
+      <c r="I29" s="178"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="175"/>
+      <c r="L29" s="174"/>
+      <c r="M29" s="175"/>
+      <c r="N29" s="174"/>
+      <c r="O29" s="175"/>
+      <c r="P29" s="169"/>
+      <c r="Q29" s="170"/>
+      <c r="R29" s="169"/>
+      <c r="S29" s="170"/>
     </row>
     <row r="30" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="267" t="s">
+      <c r="A30" s="171" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="268"/>
-      <c r="C30" s="269"/>
-      <c r="D30" s="245"/>
-      <c r="E30" s="246"/>
-      <c r="F30" s="273"/>
-      <c r="G30" s="274"/>
-      <c r="H30" s="245"/>
-      <c r="I30" s="272"/>
-      <c r="J30" s="245"/>
-      <c r="K30" s="246"/>
-      <c r="L30" s="245"/>
-      <c r="M30" s="246"/>
-      <c r="N30" s="245"/>
-      <c r="O30" s="246"/>
-      <c r="P30" s="247"/>
-      <c r="Q30" s="248"/>
-      <c r="R30" s="275"/>
-      <c r="S30" s="276"/>
+      <c r="B30" s="172"/>
+      <c r="C30" s="173"/>
+      <c r="D30" s="174"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="176"/>
+      <c r="G30" s="177"/>
+      <c r="H30" s="174"/>
+      <c r="I30" s="178"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="175"/>
+      <c r="L30" s="174"/>
+      <c r="M30" s="175"/>
+      <c r="N30" s="174"/>
+      <c r="O30" s="175"/>
+      <c r="P30" s="169"/>
+      <c r="Q30" s="170"/>
+      <c r="R30" s="179"/>
+      <c r="S30" s="180"/>
     </row>
     <row r="31" spans="1:23" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="267" t="s">
+      <c r="A31" s="171" t="s">
         <v>155</v>
       </c>
-      <c r="B31" s="268"/>
-      <c r="C31" s="269"/>
-      <c r="D31" s="245"/>
-      <c r="E31" s="246"/>
-      <c r="F31" s="270"/>
-      <c r="G31" s="271"/>
-      <c r="H31" s="245"/>
-      <c r="I31" s="272"/>
-      <c r="J31" s="245"/>
-      <c r="K31" s="246"/>
-      <c r="L31" s="245"/>
-      <c r="M31" s="246"/>
-      <c r="N31" s="245"/>
-      <c r="O31" s="246"/>
-      <c r="P31" s="247"/>
-      <c r="Q31" s="248"/>
-      <c r="R31" s="247"/>
-      <c r="S31" s="248"/>
+      <c r="B31" s="172"/>
+      <c r="C31" s="173"/>
+      <c r="D31" s="174"/>
+      <c r="E31" s="175"/>
+      <c r="F31" s="181"/>
+      <c r="G31" s="182"/>
+      <c r="H31" s="174"/>
+      <c r="I31" s="178"/>
+      <c r="J31" s="174"/>
+      <c r="K31" s="175"/>
+      <c r="L31" s="174"/>
+      <c r="M31" s="175"/>
+      <c r="N31" s="174"/>
+      <c r="O31" s="175"/>
+      <c r="P31" s="169"/>
+      <c r="Q31" s="170"/>
+      <c r="R31" s="169"/>
+      <c r="S31" s="170"/>
       <c r="U31" s="82">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="267" t="s">
+      <c r="A32" s="171" t="s">
         <v>154</v>
       </c>
-      <c r="B32" s="268"/>
-      <c r="C32" s="269"/>
-      <c r="D32" s="245"/>
-      <c r="E32" s="246"/>
-      <c r="F32" s="270"/>
-      <c r="G32" s="271"/>
-      <c r="H32" s="245"/>
-      <c r="I32" s="272"/>
-      <c r="J32" s="245"/>
-      <c r="K32" s="246"/>
-      <c r="L32" s="245"/>
-      <c r="M32" s="246"/>
-      <c r="N32" s="245"/>
-      <c r="O32" s="246"/>
-      <c r="P32" s="247"/>
-      <c r="Q32" s="248"/>
-      <c r="R32" s="247"/>
-      <c r="S32" s="248"/>
+      <c r="B32" s="172"/>
+      <c r="C32" s="173"/>
+      <c r="D32" s="174"/>
+      <c r="E32" s="175"/>
+      <c r="F32" s="181"/>
+      <c r="G32" s="182"/>
+      <c r="H32" s="174"/>
+      <c r="I32" s="178"/>
+      <c r="J32" s="174"/>
+      <c r="K32" s="175"/>
+      <c r="L32" s="174"/>
+      <c r="M32" s="175"/>
+      <c r="N32" s="174"/>
+      <c r="O32" s="175"/>
+      <c r="P32" s="169"/>
+      <c r="Q32" s="170"/>
+      <c r="R32" s="169"/>
+      <c r="S32" s="170"/>
       <c r="T32" s="81" t="s">
         <v>153</v>
       </c>
@@ -4206,27 +4206,27 @@
       </c>
     </row>
     <row r="33" spans="1:21" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="249" t="s">
+      <c r="A33" s="187" t="s">
         <v>152</v>
       </c>
-      <c r="B33" s="250"/>
-      <c r="C33" s="251"/>
-      <c r="D33" s="219"/>
-      <c r="E33" s="252"/>
-      <c r="F33" s="253"/>
-      <c r="G33" s="162"/>
-      <c r="H33" s="254"/>
-      <c r="I33" s="255"/>
-      <c r="J33" s="219"/>
-      <c r="K33" s="252"/>
-      <c r="L33" s="219"/>
-      <c r="M33" s="252"/>
-      <c r="N33" s="219"/>
-      <c r="O33" s="252"/>
-      <c r="P33" s="247"/>
-      <c r="Q33" s="248"/>
-      <c r="R33" s="247"/>
-      <c r="S33" s="248"/>
+      <c r="B33" s="188"/>
+      <c r="C33" s="189"/>
+      <c r="D33" s="183"/>
+      <c r="E33" s="184"/>
+      <c r="F33" s="190"/>
+      <c r="G33" s="191"/>
+      <c r="H33" s="192"/>
+      <c r="I33" s="193"/>
+      <c r="J33" s="183"/>
+      <c r="K33" s="184"/>
+      <c r="L33" s="183"/>
+      <c r="M33" s="184"/>
+      <c r="N33" s="183"/>
+      <c r="O33" s="184"/>
+      <c r="P33" s="169"/>
+      <c r="Q33" s="170"/>
+      <c r="R33" s="169"/>
+      <c r="S33" s="170"/>
       <c r="T33" s="79" t="s">
         <v>151</v>
       </c>
@@ -4236,42 +4236,45 @@
       </c>
     </row>
     <row r="34" spans="1:21" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="232" t="s">
+      <c r="A34" s="210" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="264"/>
-      <c r="C34" s="163"/>
-      <c r="D34" s="265">
-        <f>+SUM(D28:E33)</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="266"/>
-      <c r="F34" s="265">
-        <f>+SUM(F31:G33,F28:G29)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="266"/>
-      <c r="H34" s="265">
-        <f>+SUM(H28:I33)</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="266"/>
-      <c r="J34" s="90">
-        <v>0</v>
-      </c>
-      <c r="K34" s="91"/>
-      <c r="L34" s="92">
-        <v>0</v>
-      </c>
-      <c r="M34" s="93"/>
-      <c r="N34" s="94">
-        <v>0</v>
-      </c>
-      <c r="O34" s="95"/>
-      <c r="P34" s="221"/>
-      <c r="Q34" s="222"/>
-      <c r="R34" s="221"/>
-      <c r="S34" s="222"/>
+      <c r="B34" s="211"/>
+      <c r="C34" s="212"/>
+      <c r="D34" s="213">
+        <f>SUM(D28:E33)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="214"/>
+      <c r="F34" s="213">
+        <f>SUM(F28:G33)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="214"/>
+      <c r="H34" s="213">
+        <f>SUM(H28:I33)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="214"/>
+      <c r="J34" s="215">
+        <f>SUM(J28:K33)</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="216"/>
+      <c r="L34" s="217">
+        <f>SUM(L28:M33)</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="218"/>
+      <c r="N34" s="194">
+        <f>SUM(N28:O33)</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="195"/>
+      <c r="P34" s="196"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="196"/>
+      <c r="S34" s="197"/>
       <c r="T34" s="77" t="s">
         <v>150</v>
       </c>
@@ -4340,27 +4343,27 @@
       <c r="S37" s="23"/>
     </row>
     <row r="38" spans="1:21" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="223" t="s">
+      <c r="A38" s="227" t="s">
         <v>147</v>
       </c>
-      <c r="B38" s="224"/>
-      <c r="C38" s="224"/>
-      <c r="D38" s="224"/>
-      <c r="E38" s="224"/>
-      <c r="F38" s="224"/>
-      <c r="G38" s="224"/>
-      <c r="H38" s="224"/>
-      <c r="I38" s="224"/>
-      <c r="J38" s="224"/>
-      <c r="K38" s="224"/>
-      <c r="L38" s="224"/>
-      <c r="M38" s="224"/>
-      <c r="N38" s="224"/>
-      <c r="O38" s="224"/>
-      <c r="P38" s="224"/>
-      <c r="Q38" s="224"/>
-      <c r="R38" s="224"/>
-      <c r="S38" s="225"/>
+      <c r="B38" s="228"/>
+      <c r="C38" s="228"/>
+      <c r="D38" s="228"/>
+      <c r="E38" s="228"/>
+      <c r="F38" s="228"/>
+      <c r="G38" s="228"/>
+      <c r="H38" s="228"/>
+      <c r="I38" s="228"/>
+      <c r="J38" s="228"/>
+      <c r="K38" s="228"/>
+      <c r="L38" s="228"/>
+      <c r="M38" s="228"/>
+      <c r="N38" s="228"/>
+      <c r="O38" s="228"/>
+      <c r="P38" s="228"/>
+      <c r="Q38" s="228"/>
+      <c r="R38" s="228"/>
+      <c r="S38" s="229"/>
     </row>
     <row r="39" spans="1:21" ht="5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="67"/>
@@ -4658,942 +4661,942 @@
       <c r="Q47" s="47"/>
     </row>
     <row r="48" spans="1:21" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="226" t="s">
+      <c r="B48" s="230" t="s">
         <v>113</v>
       </c>
-      <c r="C48" s="230" t="s">
+      <c r="C48" s="234" t="s">
         <v>112</v>
       </c>
-      <c r="D48" s="231"/>
-      <c r="E48" s="156" t="s">
+      <c r="D48" s="235"/>
+      <c r="E48" s="236" t="s">
         <v>109</v>
       </c>
-      <c r="F48" s="157"/>
-      <c r="G48" s="156" t="s">
+      <c r="F48" s="237"/>
+      <c r="G48" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="H48" s="157"/>
-      <c r="K48" s="226" t="s">
+      <c r="H48" s="237"/>
+      <c r="K48" s="230" t="s">
         <v>111</v>
       </c>
-      <c r="L48" s="232" t="s">
+      <c r="L48" s="210" t="s">
         <v>110</v>
       </c>
-      <c r="M48" s="163"/>
-      <c r="N48" s="156" t="s">
+      <c r="M48" s="212"/>
+      <c r="N48" s="236" t="s">
         <v>109</v>
       </c>
-      <c r="O48" s="157"/>
-      <c r="P48" s="156" t="s">
+      <c r="O48" s="237"/>
+      <c r="P48" s="236" t="s">
         <v>108</v>
       </c>
-      <c r="Q48" s="157"/>
+      <c r="Q48" s="237"/>
     </row>
     <row r="49" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="227"/>
-      <c r="C49" s="241" t="s">
+      <c r="B49" s="231"/>
+      <c r="C49" s="185" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="242"/>
-      <c r="E49" s="256">
-        <v>0</v>
-      </c>
-      <c r="F49" s="257"/>
-      <c r="G49" s="256">
-        <v>0</v>
-      </c>
-      <c r="H49" s="257"/>
-      <c r="K49" s="228"/>
-      <c r="L49" s="258" t="s">
+      <c r="D49" s="186"/>
+      <c r="E49" s="198">
+        <v>0</v>
+      </c>
+      <c r="F49" s="199"/>
+      <c r="G49" s="198">
+        <v>0</v>
+      </c>
+      <c r="H49" s="199"/>
+      <c r="K49" s="232"/>
+      <c r="L49" s="200" t="s">
         <v>106</v>
       </c>
-      <c r="M49" s="259"/>
-      <c r="N49" s="262">
-        <v>0</v>
-      </c>
-      <c r="O49" s="263"/>
-      <c r="P49" s="262">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="263"/>
+      <c r="M49" s="201"/>
+      <c r="N49" s="204">
+        <v>0</v>
+      </c>
+      <c r="O49" s="205"/>
+      <c r="P49" s="204">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="205"/>
     </row>
     <row r="50" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="227"/>
-      <c r="C50" s="243" t="s">
+      <c r="B50" s="231"/>
+      <c r="C50" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="D50" s="244"/>
-      <c r="E50" s="207">
-        <v>0</v>
-      </c>
-      <c r="F50" s="208"/>
-      <c r="G50" s="207">
-        <v>0</v>
-      </c>
-      <c r="H50" s="208"/>
-      <c r="K50" s="228"/>
-      <c r="L50" s="260"/>
-      <c r="M50" s="261"/>
-      <c r="N50" s="235"/>
-      <c r="O50" s="236"/>
-      <c r="P50" s="235"/>
-      <c r="Q50" s="236"/>
+      <c r="D50" s="91"/>
+      <c r="E50" s="208">
+        <v>0</v>
+      </c>
+      <c r="F50" s="209"/>
+      <c r="G50" s="208">
+        <v>0</v>
+      </c>
+      <c r="H50" s="209"/>
+      <c r="K50" s="232"/>
+      <c r="L50" s="202"/>
+      <c r="M50" s="203"/>
+      <c r="N50" s="206"/>
+      <c r="O50" s="207"/>
+      <c r="P50" s="206"/>
+      <c r="Q50" s="207"/>
     </row>
     <row r="51" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="227"/>
-      <c r="C51" s="328" t="s">
+      <c r="B51" s="231"/>
+      <c r="C51" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="D51" s="329"/>
-      <c r="E51" s="207">
-        <v>0</v>
-      </c>
-      <c r="F51" s="208"/>
-      <c r="G51" s="207">
-        <v>0</v>
-      </c>
-      <c r="H51" s="208"/>
-      <c r="K51" s="228"/>
-      <c r="L51" s="237" t="s">
+      <c r="D51" s="93"/>
+      <c r="E51" s="208">
+        <v>0</v>
+      </c>
+      <c r="F51" s="209"/>
+      <c r="G51" s="208">
+        <v>0</v>
+      </c>
+      <c r="H51" s="209"/>
+      <c r="K51" s="232"/>
+      <c r="L51" s="221" t="s">
         <v>103</v>
       </c>
-      <c r="M51" s="238"/>
-      <c r="N51" s="233">
-        <v>0</v>
-      </c>
-      <c r="O51" s="234"/>
-      <c r="P51" s="233">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="234"/>
+      <c r="M51" s="222"/>
+      <c r="N51" s="225">
+        <v>0</v>
+      </c>
+      <c r="O51" s="226"/>
+      <c r="P51" s="225">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="226"/>
     </row>
     <row r="52" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="227"/>
-      <c r="C52" s="243" t="s">
+      <c r="B52" s="231"/>
+      <c r="C52" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="D52" s="244"/>
-      <c r="E52" s="207">
-        <v>0</v>
-      </c>
-      <c r="F52" s="208"/>
-      <c r="G52" s="207">
-        <v>0</v>
-      </c>
-      <c r="H52" s="208"/>
-      <c r="K52" s="228"/>
-      <c r="L52" s="239"/>
-      <c r="M52" s="240"/>
-      <c r="N52" s="235"/>
-      <c r="O52" s="236"/>
-      <c r="P52" s="235"/>
-      <c r="Q52" s="236"/>
+      <c r="D52" s="91"/>
+      <c r="E52" s="208">
+        <v>0</v>
+      </c>
+      <c r="F52" s="209"/>
+      <c r="G52" s="208">
+        <v>0</v>
+      </c>
+      <c r="H52" s="209"/>
+      <c r="K52" s="232"/>
+      <c r="L52" s="223"/>
+      <c r="M52" s="224"/>
+      <c r="N52" s="206"/>
+      <c r="O52" s="207"/>
+      <c r="P52" s="206"/>
+      <c r="Q52" s="207"/>
     </row>
     <row r="53" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="227"/>
-      <c r="C53" s="243" t="s">
+      <c r="B53" s="231"/>
+      <c r="C53" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="D53" s="244"/>
-      <c r="E53" s="207">
-        <v>0</v>
-      </c>
-      <c r="F53" s="208"/>
-      <c r="G53" s="207">
-        <v>0</v>
-      </c>
-      <c r="H53" s="208"/>
-      <c r="K53" s="228"/>
-      <c r="L53" s="217" t="s">
+      <c r="D53" s="91"/>
+      <c r="E53" s="208">
+        <v>0</v>
+      </c>
+      <c r="F53" s="209"/>
+      <c r="G53" s="208">
+        <v>0</v>
+      </c>
+      <c r="H53" s="209"/>
+      <c r="K53" s="232"/>
+      <c r="L53" s="219" t="s">
         <v>100</v>
       </c>
-      <c r="M53" s="218"/>
-      <c r="N53" s="207">
-        <v>0</v>
-      </c>
-      <c r="O53" s="208"/>
-      <c r="P53" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="208"/>
+      <c r="M53" s="220"/>
+      <c r="N53" s="208">
+        <v>0</v>
+      </c>
+      <c r="O53" s="209"/>
+      <c r="P53" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="209"/>
     </row>
     <row r="54" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="227"/>
-      <c r="C54" s="243" t="s">
+      <c r="B54" s="231"/>
+      <c r="C54" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="244"/>
-      <c r="E54" s="207">
-        <v>0</v>
-      </c>
-      <c r="F54" s="208"/>
-      <c r="G54" s="207">
-        <v>0</v>
-      </c>
-      <c r="H54" s="208"/>
-      <c r="K54" s="228"/>
-      <c r="L54" s="217" t="s">
+      <c r="D54" s="91"/>
+      <c r="E54" s="208">
+        <v>0</v>
+      </c>
+      <c r="F54" s="209"/>
+      <c r="G54" s="208">
+        <v>0</v>
+      </c>
+      <c r="H54" s="209"/>
+      <c r="K54" s="232"/>
+      <c r="L54" s="219" t="s">
         <v>98</v>
       </c>
-      <c r="M54" s="218"/>
-      <c r="N54" s="207">
-        <v>0</v>
-      </c>
-      <c r="O54" s="208"/>
-      <c r="P54" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="208"/>
+      <c r="M54" s="220"/>
+      <c r="N54" s="208">
+        <v>0</v>
+      </c>
+      <c r="O54" s="209"/>
+      <c r="P54" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="209"/>
     </row>
     <row r="55" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="227"/>
-      <c r="C55" s="243" t="s">
+      <c r="B55" s="231"/>
+      <c r="C55" s="90" t="s">
         <v>97</v>
       </c>
-      <c r="D55" s="244"/>
-      <c r="E55" s="207">
-        <v>0</v>
-      </c>
-      <c r="F55" s="208"/>
-      <c r="G55" s="207">
-        <v>0</v>
-      </c>
-      <c r="H55" s="208"/>
-      <c r="K55" s="228"/>
-      <c r="L55" s="217" t="s">
+      <c r="D55" s="91"/>
+      <c r="E55" s="208">
+        <v>0</v>
+      </c>
+      <c r="F55" s="209"/>
+      <c r="G55" s="208">
+        <v>0</v>
+      </c>
+      <c r="H55" s="209"/>
+      <c r="K55" s="232"/>
+      <c r="L55" s="219" t="s">
         <v>96</v>
       </c>
-      <c r="M55" s="218"/>
-      <c r="N55" s="207">
-        <v>0</v>
-      </c>
-      <c r="O55" s="208"/>
-      <c r="P55" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="208"/>
+      <c r="M55" s="220"/>
+      <c r="N55" s="208">
+        <v>0</v>
+      </c>
+      <c r="O55" s="209"/>
+      <c r="P55" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="209"/>
     </row>
     <row r="56" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="227"/>
-      <c r="C56" s="243" t="s">
+      <c r="B56" s="231"/>
+      <c r="C56" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="D56" s="244"/>
-      <c r="E56" s="207">
-        <v>0</v>
-      </c>
-      <c r="F56" s="208"/>
-      <c r="G56" s="207">
-        <v>0</v>
-      </c>
-      <c r="H56" s="208"/>
-      <c r="K56" s="228"/>
-      <c r="L56" s="217" t="s">
+      <c r="D56" s="91"/>
+      <c r="E56" s="208">
+        <v>0</v>
+      </c>
+      <c r="F56" s="209"/>
+      <c r="G56" s="208">
+        <v>0</v>
+      </c>
+      <c r="H56" s="209"/>
+      <c r="K56" s="232"/>
+      <c r="L56" s="219" t="s">
         <v>94</v>
       </c>
-      <c r="M56" s="218"/>
-      <c r="N56" s="207">
-        <v>0</v>
-      </c>
-      <c r="O56" s="208"/>
-      <c r="P56" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="208"/>
+      <c r="M56" s="220"/>
+      <c r="N56" s="208">
+        <v>0</v>
+      </c>
+      <c r="O56" s="209"/>
+      <c r="P56" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="209"/>
     </row>
     <row r="57" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="227"/>
-      <c r="C57" s="328" t="s">
+      <c r="B57" s="231"/>
+      <c r="C57" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="D57" s="329"/>
-      <c r="E57" s="207">
-        <v>0</v>
-      </c>
-      <c r="F57" s="208"/>
-      <c r="G57" s="207">
-        <v>0</v>
-      </c>
-      <c r="H57" s="208"/>
-      <c r="K57" s="228"/>
-      <c r="L57" s="217" t="s">
+      <c r="D57" s="93"/>
+      <c r="E57" s="208">
+        <v>0</v>
+      </c>
+      <c r="F57" s="209"/>
+      <c r="G57" s="208">
+        <v>0</v>
+      </c>
+      <c r="H57" s="209"/>
+      <c r="K57" s="232"/>
+      <c r="L57" s="219" t="s">
         <v>92</v>
       </c>
-      <c r="M57" s="218"/>
-      <c r="N57" s="207">
-        <v>0</v>
-      </c>
-      <c r="O57" s="208"/>
-      <c r="P57" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="208"/>
+      <c r="M57" s="220"/>
+      <c r="N57" s="208">
+        <v>0</v>
+      </c>
+      <c r="O57" s="209"/>
+      <c r="P57" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="209"/>
     </row>
     <row r="58" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="227"/>
-      <c r="C58" s="243" t="s">
+      <c r="B58" s="231"/>
+      <c r="C58" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="D58" s="244"/>
-      <c r="E58" s="207">
-        <v>0</v>
-      </c>
-      <c r="F58" s="208"/>
-      <c r="G58" s="207">
-        <v>0</v>
-      </c>
-      <c r="H58" s="208"/>
-      <c r="K58" s="228"/>
-      <c r="L58" s="217" t="s">
+      <c r="D58" s="91"/>
+      <c r="E58" s="208">
+        <v>0</v>
+      </c>
+      <c r="F58" s="209"/>
+      <c r="G58" s="208">
+        <v>0</v>
+      </c>
+      <c r="H58" s="209"/>
+      <c r="K58" s="232"/>
+      <c r="L58" s="219" t="s">
         <v>90</v>
       </c>
-      <c r="M58" s="218"/>
-      <c r="N58" s="207">
-        <v>0</v>
-      </c>
-      <c r="O58" s="208"/>
-      <c r="P58" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="208"/>
+      <c r="M58" s="220"/>
+      <c r="N58" s="208">
+        <v>0</v>
+      </c>
+      <c r="O58" s="209"/>
+      <c r="P58" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="209"/>
     </row>
     <row r="59" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="227"/>
-      <c r="C59" s="243" t="s">
+      <c r="B59" s="231"/>
+      <c r="C59" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="D59" s="244"/>
-      <c r="E59" s="207">
-        <v>0</v>
-      </c>
-      <c r="F59" s="208"/>
-      <c r="G59" s="207">
-        <v>0</v>
-      </c>
-      <c r="H59" s="208"/>
-      <c r="K59" s="228"/>
-      <c r="L59" s="217" t="s">
+      <c r="D59" s="91"/>
+      <c r="E59" s="208">
+        <v>0</v>
+      </c>
+      <c r="F59" s="209"/>
+      <c r="G59" s="208">
+        <v>0</v>
+      </c>
+      <c r="H59" s="209"/>
+      <c r="K59" s="232"/>
+      <c r="L59" s="219" t="s">
         <v>88</v>
       </c>
-      <c r="M59" s="218"/>
-      <c r="N59" s="207">
-        <v>0</v>
-      </c>
-      <c r="O59" s="208"/>
-      <c r="P59" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="208"/>
+      <c r="M59" s="220"/>
+      <c r="N59" s="208">
+        <v>0</v>
+      </c>
+      <c r="O59" s="209"/>
+      <c r="P59" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="209"/>
     </row>
     <row r="60" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="227"/>
-      <c r="C60" s="243" t="s">
+      <c r="B60" s="231"/>
+      <c r="C60" s="90" t="s">
         <v>87</v>
       </c>
-      <c r="D60" s="244"/>
-      <c r="E60" s="207">
-        <v>0</v>
-      </c>
-      <c r="F60" s="208"/>
-      <c r="G60" s="207">
-        <v>0</v>
-      </c>
-      <c r="H60" s="208"/>
-      <c r="K60" s="228"/>
-      <c r="L60" s="217" t="s">
+      <c r="D60" s="91"/>
+      <c r="E60" s="208">
+        <v>0</v>
+      </c>
+      <c r="F60" s="209"/>
+      <c r="G60" s="208">
+        <v>0</v>
+      </c>
+      <c r="H60" s="209"/>
+      <c r="K60" s="232"/>
+      <c r="L60" s="219" t="s">
         <v>86</v>
       </c>
-      <c r="M60" s="218"/>
-      <c r="N60" s="207">
-        <v>0</v>
-      </c>
-      <c r="O60" s="208"/>
-      <c r="P60" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="208"/>
+      <c r="M60" s="220"/>
+      <c r="N60" s="208">
+        <v>0</v>
+      </c>
+      <c r="O60" s="209"/>
+      <c r="P60" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="209"/>
     </row>
     <row r="61" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="227"/>
-      <c r="C61" s="243" t="s">
+      <c r="B61" s="231"/>
+      <c r="C61" s="90" t="s">
         <v>85</v>
       </c>
-      <c r="D61" s="244"/>
-      <c r="E61" s="207">
-        <v>0</v>
-      </c>
-      <c r="F61" s="208"/>
-      <c r="G61" s="207">
-        <v>0</v>
-      </c>
-      <c r="H61" s="208"/>
-      <c r="K61" s="228"/>
-      <c r="L61" s="217" t="s">
+      <c r="D61" s="91"/>
+      <c r="E61" s="208">
+        <v>0</v>
+      </c>
+      <c r="F61" s="209"/>
+      <c r="G61" s="208">
+        <v>0</v>
+      </c>
+      <c r="H61" s="209"/>
+      <c r="K61" s="232"/>
+      <c r="L61" s="219" t="s">
         <v>84</v>
       </c>
-      <c r="M61" s="218"/>
-      <c r="N61" s="207">
-        <v>0</v>
-      </c>
-      <c r="O61" s="208"/>
-      <c r="P61" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="208"/>
+      <c r="M61" s="220"/>
+      <c r="N61" s="208">
+        <v>0</v>
+      </c>
+      <c r="O61" s="209"/>
+      <c r="P61" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="209"/>
     </row>
     <row r="62" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="227"/>
-      <c r="C62" s="243" t="s">
+      <c r="B62" s="231"/>
+      <c r="C62" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="D62" s="244"/>
-      <c r="E62" s="207">
-        <v>0</v>
-      </c>
-      <c r="F62" s="208"/>
-      <c r="G62" s="207">
-        <v>0</v>
-      </c>
-      <c r="H62" s="208"/>
-      <c r="K62" s="228"/>
-      <c r="L62" s="217" t="s">
+      <c r="D62" s="91"/>
+      <c r="E62" s="208">
+        <v>0</v>
+      </c>
+      <c r="F62" s="209"/>
+      <c r="G62" s="208">
+        <v>0</v>
+      </c>
+      <c r="H62" s="209"/>
+      <c r="K62" s="232"/>
+      <c r="L62" s="219" t="s">
         <v>82</v>
       </c>
-      <c r="M62" s="218"/>
-      <c r="N62" s="207">
-        <v>0</v>
-      </c>
-      <c r="O62" s="208"/>
-      <c r="P62" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="208"/>
+      <c r="M62" s="220"/>
+      <c r="N62" s="208">
+        <v>0</v>
+      </c>
+      <c r="O62" s="209"/>
+      <c r="P62" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="209"/>
     </row>
     <row r="63" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="227"/>
-      <c r="C63" s="243" t="s">
+      <c r="B63" s="231"/>
+      <c r="C63" s="90" t="s">
         <v>81</v>
       </c>
-      <c r="D63" s="244"/>
-      <c r="E63" s="207">
-        <v>0</v>
-      </c>
-      <c r="F63" s="208"/>
-      <c r="G63" s="207">
-        <v>0</v>
-      </c>
-      <c r="H63" s="208"/>
-      <c r="K63" s="228"/>
-      <c r="L63" s="217" t="s">
+      <c r="D63" s="91"/>
+      <c r="E63" s="208">
+        <v>0</v>
+      </c>
+      <c r="F63" s="209"/>
+      <c r="G63" s="208">
+        <v>0</v>
+      </c>
+      <c r="H63" s="209"/>
+      <c r="K63" s="232"/>
+      <c r="L63" s="219" t="s">
         <v>80</v>
       </c>
-      <c r="M63" s="218"/>
-      <c r="N63" s="207">
-        <v>0</v>
-      </c>
-      <c r="O63" s="208"/>
-      <c r="P63" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="208"/>
+      <c r="M63" s="220"/>
+      <c r="N63" s="208">
+        <v>0</v>
+      </c>
+      <c r="O63" s="209"/>
+      <c r="P63" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="209"/>
     </row>
     <row r="64" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="227"/>
-      <c r="C64" s="328" t="s">
+      <c r="B64" s="231"/>
+      <c r="C64" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="D64" s="329"/>
-      <c r="E64" s="207">
-        <v>0</v>
-      </c>
-      <c r="F64" s="208"/>
-      <c r="G64" s="207">
-        <v>0</v>
-      </c>
-      <c r="H64" s="208"/>
-      <c r="K64" s="228"/>
-      <c r="L64" s="217" t="s">
+      <c r="D64" s="93"/>
+      <c r="E64" s="208">
+        <v>0</v>
+      </c>
+      <c r="F64" s="209"/>
+      <c r="G64" s="208">
+        <v>0</v>
+      </c>
+      <c r="H64" s="209"/>
+      <c r="K64" s="232"/>
+      <c r="L64" s="219" t="s">
         <v>78</v>
       </c>
-      <c r="M64" s="218"/>
-      <c r="N64" s="207">
-        <v>0</v>
-      </c>
-      <c r="O64" s="208"/>
-      <c r="P64" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="208"/>
+      <c r="M64" s="220"/>
+      <c r="N64" s="208">
+        <v>0</v>
+      </c>
+      <c r="O64" s="209"/>
+      <c r="P64" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="209"/>
     </row>
     <row r="65" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="227"/>
-      <c r="C65" s="243" t="s">
+      <c r="B65" s="231"/>
+      <c r="C65" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="D65" s="244"/>
-      <c r="E65" s="207">
-        <v>0</v>
-      </c>
-      <c r="F65" s="208"/>
-      <c r="G65" s="207">
-        <v>0</v>
-      </c>
-      <c r="H65" s="208"/>
-      <c r="K65" s="228"/>
-      <c r="L65" s="217" t="s">
+      <c r="D65" s="91"/>
+      <c r="E65" s="208">
+        <v>0</v>
+      </c>
+      <c r="F65" s="209"/>
+      <c r="G65" s="208">
+        <v>0</v>
+      </c>
+      <c r="H65" s="209"/>
+      <c r="K65" s="232"/>
+      <c r="L65" s="219" t="s">
         <v>76</v>
       </c>
-      <c r="M65" s="218"/>
-      <c r="N65" s="207">
-        <v>0</v>
-      </c>
-      <c r="O65" s="208"/>
-      <c r="P65" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="208"/>
+      <c r="M65" s="220"/>
+      <c r="N65" s="208">
+        <v>0</v>
+      </c>
+      <c r="O65" s="209"/>
+      <c r="P65" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="209"/>
     </row>
     <row r="66" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="227"/>
-      <c r="C66" s="243" t="s">
+      <c r="B66" s="231"/>
+      <c r="C66" s="90" t="s">
         <v>75</v>
       </c>
-      <c r="D66" s="244"/>
-      <c r="E66" s="207">
-        <v>0</v>
-      </c>
-      <c r="F66" s="208"/>
-      <c r="G66" s="207">
-        <v>0</v>
-      </c>
-      <c r="H66" s="208"/>
-      <c r="K66" s="228"/>
-      <c r="L66" s="217" t="s">
+      <c r="D66" s="91"/>
+      <c r="E66" s="208">
+        <v>0</v>
+      </c>
+      <c r="F66" s="209"/>
+      <c r="G66" s="208">
+        <v>0</v>
+      </c>
+      <c r="H66" s="209"/>
+      <c r="K66" s="232"/>
+      <c r="L66" s="219" t="s">
         <v>74</v>
       </c>
-      <c r="M66" s="218"/>
-      <c r="N66" s="207">
-        <v>0</v>
-      </c>
-      <c r="O66" s="208"/>
-      <c r="P66" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="208"/>
+      <c r="M66" s="220"/>
+      <c r="N66" s="208">
+        <v>0</v>
+      </c>
+      <c r="O66" s="209"/>
+      <c r="P66" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="209"/>
     </row>
     <row r="67" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="227"/>
-      <c r="C67" s="243" t="s">
+      <c r="B67" s="231"/>
+      <c r="C67" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="D67" s="244"/>
-      <c r="E67" s="207">
-        <v>0</v>
-      </c>
-      <c r="F67" s="208"/>
-      <c r="G67" s="207">
-        <v>0</v>
-      </c>
-      <c r="H67" s="208"/>
-      <c r="K67" s="228"/>
-      <c r="L67" s="217" t="s">
+      <c r="D67" s="91"/>
+      <c r="E67" s="208">
+        <v>0</v>
+      </c>
+      <c r="F67" s="209"/>
+      <c r="G67" s="208">
+        <v>0</v>
+      </c>
+      <c r="H67" s="209"/>
+      <c r="K67" s="232"/>
+      <c r="L67" s="219" t="s">
         <v>72</v>
       </c>
-      <c r="M67" s="218"/>
-      <c r="N67" s="207">
-        <v>0</v>
-      </c>
-      <c r="O67" s="208"/>
-      <c r="P67" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="208"/>
+      <c r="M67" s="220"/>
+      <c r="N67" s="208">
+        <v>0</v>
+      </c>
+      <c r="O67" s="209"/>
+      <c r="P67" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="209"/>
     </row>
     <row r="68" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="227"/>
-      <c r="C68" s="243" t="s">
+      <c r="B68" s="231"/>
+      <c r="C68" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="D68" s="244"/>
-      <c r="E68" s="207">
-        <v>0</v>
-      </c>
-      <c r="F68" s="208"/>
-      <c r="G68" s="207">
-        <v>0</v>
-      </c>
-      <c r="H68" s="208"/>
-      <c r="K68" s="228"/>
-      <c r="L68" s="217" t="s">
+      <c r="D68" s="91"/>
+      <c r="E68" s="208">
+        <v>0</v>
+      </c>
+      <c r="F68" s="209"/>
+      <c r="G68" s="208">
+        <v>0</v>
+      </c>
+      <c r="H68" s="209"/>
+      <c r="K68" s="232"/>
+      <c r="L68" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="M68" s="218"/>
-      <c r="N68" s="207">
-        <v>0</v>
-      </c>
-      <c r="O68" s="208"/>
-      <c r="P68" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="208"/>
+      <c r="M68" s="220"/>
+      <c r="N68" s="208">
+        <v>0</v>
+      </c>
+      <c r="O68" s="209"/>
+      <c r="P68" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="209"/>
     </row>
     <row r="69" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B69" s="227"/>
-      <c r="C69" s="243" t="s">
+      <c r="B69" s="231"/>
+      <c r="C69" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="D69" s="244"/>
-      <c r="E69" s="207">
-        <v>0</v>
-      </c>
-      <c r="F69" s="208"/>
-      <c r="G69" s="207">
-        <v>0</v>
-      </c>
-      <c r="H69" s="208"/>
-      <c r="K69" s="228"/>
-      <c r="L69" s="217" t="s">
+      <c r="D69" s="91"/>
+      <c r="E69" s="208">
+        <v>0</v>
+      </c>
+      <c r="F69" s="209"/>
+      <c r="G69" s="208">
+        <v>0</v>
+      </c>
+      <c r="H69" s="209"/>
+      <c r="K69" s="232"/>
+      <c r="L69" s="219" t="s">
         <v>68</v>
       </c>
-      <c r="M69" s="218"/>
-      <c r="N69" s="207">
-        <v>0</v>
-      </c>
-      <c r="O69" s="208"/>
-      <c r="P69" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="208"/>
+      <c r="M69" s="220"/>
+      <c r="N69" s="208">
+        <v>0</v>
+      </c>
+      <c r="O69" s="209"/>
+      <c r="P69" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="209"/>
     </row>
     <row r="70" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B70" s="227"/>
-      <c r="C70" s="328" t="s">
+      <c r="B70" s="231"/>
+      <c r="C70" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="D70" s="329"/>
-      <c r="E70" s="207">
-        <v>0</v>
-      </c>
-      <c r="F70" s="208"/>
-      <c r="G70" s="207">
-        <v>0</v>
-      </c>
-      <c r="H70" s="208"/>
-      <c r="K70" s="228"/>
-      <c r="L70" s="217" t="s">
+      <c r="D70" s="93"/>
+      <c r="E70" s="208">
+        <v>0</v>
+      </c>
+      <c r="F70" s="209"/>
+      <c r="G70" s="208">
+        <v>0</v>
+      </c>
+      <c r="H70" s="209"/>
+      <c r="K70" s="232"/>
+      <c r="L70" s="219" t="s">
         <v>66</v>
       </c>
-      <c r="M70" s="218"/>
-      <c r="N70" s="207">
-        <v>0</v>
-      </c>
-      <c r="O70" s="208"/>
-      <c r="P70" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="208"/>
+      <c r="M70" s="220"/>
+      <c r="N70" s="208">
+        <v>0</v>
+      </c>
+      <c r="O70" s="209"/>
+      <c r="P70" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="209"/>
     </row>
     <row r="71" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B71" s="227"/>
-      <c r="C71" s="347" t="s">
+      <c r="B71" s="231"/>
+      <c r="C71" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="D71" s="348"/>
-      <c r="E71" s="207">
-        <v>0</v>
-      </c>
-      <c r="F71" s="208"/>
-      <c r="G71" s="207">
-        <v>0</v>
-      </c>
-      <c r="H71" s="208"/>
-      <c r="K71" s="228"/>
-      <c r="L71" s="217" t="s">
+      <c r="D71" s="99"/>
+      <c r="E71" s="208">
+        <v>0</v>
+      </c>
+      <c r="F71" s="209"/>
+      <c r="G71" s="208">
+        <v>0</v>
+      </c>
+      <c r="H71" s="209"/>
+      <c r="K71" s="232"/>
+      <c r="L71" s="219" t="s">
         <v>64</v>
       </c>
-      <c r="M71" s="218"/>
-      <c r="N71" s="207">
-        <v>0</v>
-      </c>
-      <c r="O71" s="208"/>
-      <c r="P71" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="208"/>
+      <c r="M71" s="220"/>
+      <c r="N71" s="208">
+        <v>0</v>
+      </c>
+      <c r="O71" s="209"/>
+      <c r="P71" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="209"/>
     </row>
     <row r="72" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B72" s="227"/>
-      <c r="C72" s="328" t="s">
+      <c r="B72" s="231"/>
+      <c r="C72" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="D72" s="329"/>
-      <c r="E72" s="207">
-        <v>0</v>
-      </c>
-      <c r="F72" s="208"/>
-      <c r="G72" s="207">
-        <v>0</v>
-      </c>
-      <c r="H72" s="208"/>
-      <c r="K72" s="228"/>
-      <c r="L72" s="217" t="s">
+      <c r="D72" s="93"/>
+      <c r="E72" s="208">
+        <v>0</v>
+      </c>
+      <c r="F72" s="209"/>
+      <c r="G72" s="208">
+        <v>0</v>
+      </c>
+      <c r="H72" s="209"/>
+      <c r="K72" s="232"/>
+      <c r="L72" s="219" t="s">
         <v>62</v>
       </c>
-      <c r="M72" s="218"/>
-      <c r="N72" s="207">
-        <v>0</v>
-      </c>
-      <c r="O72" s="208"/>
-      <c r="P72" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="208"/>
+      <c r="M72" s="220"/>
+      <c r="N72" s="208">
+        <v>0</v>
+      </c>
+      <c r="O72" s="209"/>
+      <c r="P72" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="209"/>
     </row>
     <row r="73" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="227"/>
-      <c r="C73" s="328" t="s">
+      <c r="B73" s="231"/>
+      <c r="C73" s="92" t="s">
         <v>61</v>
       </c>
-      <c r="D73" s="329"/>
-      <c r="E73" s="207">
-        <v>0</v>
-      </c>
-      <c r="F73" s="208"/>
-      <c r="G73" s="207">
-        <v>0</v>
-      </c>
-      <c r="H73" s="208"/>
-      <c r="K73" s="228"/>
-      <c r="L73" s="217" t="s">
+      <c r="D73" s="93"/>
+      <c r="E73" s="208">
+        <v>0</v>
+      </c>
+      <c r="F73" s="209"/>
+      <c r="G73" s="208">
+        <v>0</v>
+      </c>
+      <c r="H73" s="209"/>
+      <c r="K73" s="232"/>
+      <c r="L73" s="219" t="s">
         <v>60</v>
       </c>
-      <c r="M73" s="218"/>
-      <c r="N73" s="207">
-        <v>0</v>
-      </c>
-      <c r="O73" s="208"/>
-      <c r="P73" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="208"/>
+      <c r="M73" s="220"/>
+      <c r="N73" s="208">
+        <v>0</v>
+      </c>
+      <c r="O73" s="209"/>
+      <c r="P73" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="209"/>
     </row>
     <row r="74" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="227"/>
-      <c r="C74" s="328" t="s">
+      <c r="B74" s="231"/>
+      <c r="C74" s="92" t="s">
         <v>59</v>
       </c>
-      <c r="D74" s="329"/>
-      <c r="E74" s="207">
-        <v>0</v>
-      </c>
-      <c r="F74" s="208"/>
-      <c r="G74" s="207">
-        <v>0</v>
-      </c>
-      <c r="H74" s="208"/>
-      <c r="K74" s="228"/>
-      <c r="L74" s="217" t="s">
+      <c r="D74" s="93"/>
+      <c r="E74" s="208">
+        <v>0</v>
+      </c>
+      <c r="F74" s="209"/>
+      <c r="G74" s="208">
+        <v>0</v>
+      </c>
+      <c r="H74" s="209"/>
+      <c r="K74" s="232"/>
+      <c r="L74" s="219" t="s">
         <v>58</v>
       </c>
-      <c r="M74" s="218"/>
-      <c r="N74" s="207">
-        <v>0</v>
-      </c>
-      <c r="O74" s="208"/>
-      <c r="P74" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="208"/>
+      <c r="M74" s="220"/>
+      <c r="N74" s="208">
+        <v>0</v>
+      </c>
+      <c r="O74" s="209"/>
+      <c r="P74" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="209"/>
     </row>
     <row r="75" spans="2:17" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="227"/>
-      <c r="C75" s="243" t="s">
+      <c r="B75" s="231"/>
+      <c r="C75" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="D75" s="244"/>
-      <c r="E75" s="207">
-        <v>0</v>
-      </c>
-      <c r="F75" s="208"/>
-      <c r="G75" s="207">
-        <v>0</v>
-      </c>
-      <c r="H75" s="208"/>
-      <c r="K75" s="228"/>
-      <c r="L75" s="217" t="s">
+      <c r="D75" s="91"/>
+      <c r="E75" s="208">
+        <v>0</v>
+      </c>
+      <c r="F75" s="209"/>
+      <c r="G75" s="208">
+        <v>0</v>
+      </c>
+      <c r="H75" s="209"/>
+      <c r="K75" s="232"/>
+      <c r="L75" s="219" t="s">
         <v>56</v>
       </c>
-      <c r="M75" s="218"/>
-      <c r="N75" s="219">
-        <v>0</v>
-      </c>
-      <c r="O75" s="220"/>
-      <c r="P75" s="207">
-        <v>0</v>
-      </c>
-      <c r="Q75" s="208"/>
+      <c r="M75" s="220"/>
+      <c r="N75" s="183">
+        <v>0</v>
+      </c>
+      <c r="O75" s="238"/>
+      <c r="P75" s="208">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="209"/>
     </row>
     <row r="76" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B76" s="227"/>
-      <c r="C76" s="243" t="s">
+      <c r="B76" s="231"/>
+      <c r="C76" s="90" t="s">
         <v>55</v>
       </c>
-      <c r="D76" s="244"/>
-      <c r="E76" s="207">
-        <v>0</v>
-      </c>
-      <c r="F76" s="208"/>
-      <c r="G76" s="207">
-        <v>0</v>
-      </c>
-      <c r="H76" s="208"/>
-      <c r="K76" s="228"/>
-      <c r="L76" s="209" t="s">
+      <c r="D76" s="91"/>
+      <c r="E76" s="208">
+        <v>0</v>
+      </c>
+      <c r="F76" s="209"/>
+      <c r="G76" s="208">
+        <v>0</v>
+      </c>
+      <c r="H76" s="209"/>
+      <c r="K76" s="232"/>
+      <c r="L76" s="239" t="s">
         <v>54</v>
       </c>
-      <c r="M76" s="210"/>
-      <c r="N76" s="211">
-        <v>0</v>
-      </c>
-      <c r="O76" s="212"/>
-      <c r="P76" s="184">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="185"/>
+      <c r="M76" s="240"/>
+      <c r="N76" s="243">
+        <v>0</v>
+      </c>
+      <c r="O76" s="244"/>
+      <c r="P76" s="247">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="248"/>
     </row>
     <row r="77" spans="2:17" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="227"/>
-      <c r="C77" s="351" t="s">
+      <c r="B77" s="231"/>
+      <c r="C77" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="D77" s="352"/>
-      <c r="E77" s="215">
-        <v>0</v>
-      </c>
-      <c r="F77" s="216"/>
-      <c r="G77" s="215">
-        <v>0</v>
-      </c>
-      <c r="H77" s="216"/>
-      <c r="K77" s="229"/>
-      <c r="L77" s="178"/>
-      <c r="M77" s="179"/>
-      <c r="N77" s="213"/>
-      <c r="O77" s="214"/>
-      <c r="P77" s="186"/>
-      <c r="Q77" s="148"/>
+      <c r="D77" s="97"/>
+      <c r="E77" s="251">
+        <v>0</v>
+      </c>
+      <c r="F77" s="252"/>
+      <c r="G77" s="251">
+        <v>0</v>
+      </c>
+      <c r="H77" s="252"/>
+      <c r="K77" s="233"/>
+      <c r="L77" s="241"/>
+      <c r="M77" s="242"/>
+      <c r="N77" s="245"/>
+      <c r="O77" s="246"/>
+      <c r="P77" s="249"/>
+      <c r="Q77" s="250"/>
     </row>
     <row r="78" spans="2:17" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="227"/>
-      <c r="C78" s="351" t="s">
+      <c r="B78" s="231"/>
+      <c r="C78" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="D78" s="352"/>
-      <c r="E78" s="215">
-        <v>0</v>
-      </c>
-      <c r="F78" s="216"/>
-      <c r="G78" s="215">
-        <v>0</v>
-      </c>
-      <c r="H78" s="216"/>
+      <c r="D78" s="97"/>
+      <c r="E78" s="251">
+        <v>0</v>
+      </c>
+      <c r="F78" s="252"/>
+      <c r="G78" s="251">
+        <v>0</v>
+      </c>
+      <c r="H78" s="252"/>
     </row>
     <row r="79" spans="2:17" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="227"/>
-      <c r="C79" s="351" t="s">
+      <c r="B79" s="231"/>
+      <c r="C79" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="D79" s="352"/>
-      <c r="E79" s="189">
-        <v>0</v>
-      </c>
-      <c r="F79" s="190"/>
-      <c r="G79" s="189">
-        <v>0</v>
-      </c>
-      <c r="H79" s="190"/>
-      <c r="K79" s="191" t="s">
+      <c r="D79" s="97"/>
+      <c r="E79" s="253">
+        <v>0</v>
+      </c>
+      <c r="F79" s="254"/>
+      <c r="G79" s="253">
+        <v>0</v>
+      </c>
+      <c r="H79" s="254"/>
+      <c r="K79" s="255" t="s">
         <v>50</v>
       </c>
-      <c r="L79" s="192"/>
-      <c r="M79" s="193"/>
-      <c r="N79" s="197">
+      <c r="L79" s="256"/>
+      <c r="M79" s="257"/>
+      <c r="N79" s="261">
         <f>+E82+N76</f>
         <v>0</v>
       </c>
-      <c r="O79" s="198"/>
-      <c r="P79" s="201">
+      <c r="O79" s="262"/>
+      <c r="P79" s="265">
         <f>+G82+P76</f>
         <v>0</v>
       </c>
-      <c r="Q79" s="202"/>
+      <c r="Q79" s="266"/>
     </row>
     <row r="80" spans="2:17" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="227"/>
-      <c r="C80" s="351" t="s">
+      <c r="B80" s="231"/>
+      <c r="C80" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="D80" s="352"/>
-      <c r="E80" s="189">
-        <v>0</v>
-      </c>
-      <c r="F80" s="190"/>
-      <c r="G80" s="189">
-        <v>0</v>
-      </c>
-      <c r="H80" s="190"/>
-      <c r="K80" s="194"/>
-      <c r="L80" s="195"/>
-      <c r="M80" s="196"/>
-      <c r="N80" s="199"/>
-      <c r="O80" s="200"/>
-      <c r="P80" s="203"/>
-      <c r="Q80" s="204"/>
+      <c r="D80" s="97"/>
+      <c r="E80" s="253">
+        <v>0</v>
+      </c>
+      <c r="F80" s="254"/>
+      <c r="G80" s="253">
+        <v>0</v>
+      </c>
+      <c r="H80" s="254"/>
+      <c r="K80" s="258"/>
+      <c r="L80" s="259"/>
+      <c r="M80" s="260"/>
+      <c r="N80" s="263"/>
+      <c r="O80" s="264"/>
+      <c r="P80" s="267"/>
+      <c r="Q80" s="268"/>
     </row>
     <row r="81" spans="1:21" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="227"/>
-      <c r="C81" s="349" t="s">
+      <c r="B81" s="231"/>
+      <c r="C81" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="D81" s="350"/>
-      <c r="E81" s="205">
-        <v>0</v>
-      </c>
-      <c r="F81" s="206"/>
-      <c r="G81" s="205">
-        <v>0</v>
-      </c>
-      <c r="H81" s="206"/>
+      <c r="D81" s="95"/>
+      <c r="E81" s="269">
+        <v>0</v>
+      </c>
+      <c r="F81" s="270"/>
+      <c r="G81" s="269">
+        <v>0</v>
+      </c>
+      <c r="H81" s="270"/>
       <c r="L81" s="28"/>
       <c r="M81" s="44"/>
       <c r="N81" s="44"/>
     </row>
     <row r="82" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="228"/>
-      <c r="C82" s="176" t="s">
+      <c r="B82" s="232"/>
+      <c r="C82" s="277" t="s">
         <v>47</v>
       </c>
-      <c r="D82" s="177"/>
-      <c r="E82" s="180">
-        <v>0</v>
-      </c>
-      <c r="F82" s="181"/>
-      <c r="G82" s="184">
-        <v>0</v>
-      </c>
-      <c r="H82" s="185"/>
+      <c r="D82" s="278"/>
+      <c r="E82" s="279">
+        <v>0</v>
+      </c>
+      <c r="F82" s="280"/>
+      <c r="G82" s="247">
+        <v>0</v>
+      </c>
+      <c r="H82" s="248"/>
       <c r="N82" s="28"/>
       <c r="O82" s="44"/>
       <c r="P82" s="44"/>
     </row>
     <row r="83" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="229"/>
-      <c r="C83" s="178"/>
-      <c r="D83" s="179"/>
-      <c r="E83" s="182"/>
-      <c r="F83" s="183"/>
-      <c r="G83" s="186"/>
-      <c r="H83" s="148"/>
+      <c r="B83" s="233"/>
+      <c r="C83" s="241"/>
+      <c r="D83" s="242"/>
+      <c r="E83" s="281"/>
+      <c r="F83" s="282"/>
+      <c r="G83" s="249"/>
+      <c r="H83" s="250"/>
       <c r="O83" s="44"/>
       <c r="P83" s="44"/>
     </row>
@@ -5664,206 +5667,206 @@
       <c r="A87" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B87" s="187" t="s">
+      <c r="B87" s="283" t="s">
         <v>43</v>
       </c>
-      <c r="C87" s="188"/>
-      <c r="D87" s="170" t="s">
+      <c r="C87" s="284"/>
+      <c r="D87" s="271" t="s">
         <v>42</v>
       </c>
-      <c r="E87" s="171"/>
-      <c r="F87" s="170" t="s">
+      <c r="E87" s="272"/>
+      <c r="F87" s="271" t="s">
         <v>41</v>
       </c>
-      <c r="G87" s="171"/>
-      <c r="H87" s="170" t="s">
+      <c r="G87" s="272"/>
+      <c r="H87" s="271" t="s">
         <v>40</v>
       </c>
-      <c r="I87" s="171"/>
-      <c r="J87" s="170" t="s">
+      <c r="I87" s="272"/>
+      <c r="J87" s="271" t="s">
         <v>39</v>
       </c>
-      <c r="K87" s="171"/>
-      <c r="L87" s="170" t="s">
+      <c r="K87" s="272"/>
+      <c r="L87" s="271" t="s">
         <v>38</v>
       </c>
-      <c r="M87" s="171"/>
-      <c r="N87" s="170" t="s">
+      <c r="M87" s="272"/>
+      <c r="N87" s="271" t="s">
         <v>37</v>
       </c>
-      <c r="O87" s="171"/>
-      <c r="P87" s="170" t="s">
+      <c r="O87" s="272"/>
+      <c r="P87" s="271" t="s">
         <v>36</v>
       </c>
-      <c r="Q87" s="171"/>
-      <c r="R87" s="170" t="s">
+      <c r="Q87" s="272"/>
+      <c r="R87" s="271" t="s">
         <v>35</v>
       </c>
-      <c r="S87" s="171"/>
-      <c r="T87" s="170" t="s">
+      <c r="S87" s="272"/>
+      <c r="T87" s="271" t="s">
         <v>34</v>
       </c>
-      <c r="U87" s="171"/>
+      <c r="U87" s="272"/>
     </row>
     <row r="88" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B88" s="172">
-        <v>0</v>
-      </c>
-      <c r="C88" s="173"/>
-      <c r="D88" s="174">
-        <v>0</v>
-      </c>
-      <c r="E88" s="169"/>
-      <c r="F88" s="169">
-        <v>0</v>
-      </c>
-      <c r="G88" s="169"/>
-      <c r="H88" s="169">
-        <v>0</v>
-      </c>
-      <c r="I88" s="169"/>
-      <c r="J88" s="169">
-        <v>0</v>
-      </c>
-      <c r="K88" s="169"/>
-      <c r="L88" s="169">
-        <v>0</v>
-      </c>
-      <c r="M88" s="169"/>
-      <c r="N88" s="169">
-        <v>0</v>
-      </c>
-      <c r="O88" s="169"/>
-      <c r="P88" s="169">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="169"/>
-      <c r="R88" s="169">
-        <v>0</v>
-      </c>
-      <c r="S88" s="169"/>
-      <c r="T88" s="169">
-        <v>0</v>
-      </c>
-      <c r="U88" s="175"/>
+      <c r="B88" s="273">
+        <v>0</v>
+      </c>
+      <c r="C88" s="274"/>
+      <c r="D88" s="275">
+        <v>0</v>
+      </c>
+      <c r="E88" s="276"/>
+      <c r="F88" s="276">
+        <v>0</v>
+      </c>
+      <c r="G88" s="276"/>
+      <c r="H88" s="276">
+        <v>0</v>
+      </c>
+      <c r="I88" s="276"/>
+      <c r="J88" s="276">
+        <v>0</v>
+      </c>
+      <c r="K88" s="276"/>
+      <c r="L88" s="276">
+        <v>0</v>
+      </c>
+      <c r="M88" s="276"/>
+      <c r="N88" s="276">
+        <v>0</v>
+      </c>
+      <c r="O88" s="276"/>
+      <c r="P88" s="276">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="276"/>
+      <c r="R88" s="276">
+        <v>0</v>
+      </c>
+      <c r="S88" s="276"/>
+      <c r="T88" s="276">
+        <v>0</v>
+      </c>
+      <c r="U88" s="167"/>
     </row>
     <row r="89" spans="1:21" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A89" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="B89" s="166">
-        <v>0</v>
-      </c>
-      <c r="C89" s="167"/>
-      <c r="D89" s="168">
-        <v>0</v>
-      </c>
-      <c r="E89" s="161"/>
-      <c r="F89" s="161">
-        <v>0</v>
-      </c>
-      <c r="G89" s="161"/>
-      <c r="H89" s="161">
-        <v>0</v>
-      </c>
-      <c r="I89" s="161"/>
-      <c r="J89" s="161">
-        <v>0</v>
-      </c>
-      <c r="K89" s="161"/>
-      <c r="L89" s="161">
-        <v>0</v>
-      </c>
-      <c r="M89" s="161"/>
-      <c r="N89" s="161">
-        <v>0</v>
-      </c>
-      <c r="O89" s="161"/>
-      <c r="P89" s="161">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="161"/>
-      <c r="R89" s="161">
-        <v>0</v>
-      </c>
-      <c r="S89" s="161"/>
-      <c r="T89" s="161">
-        <v>0</v>
-      </c>
-      <c r="U89" s="162"/>
+      <c r="B89" s="291">
+        <v>0</v>
+      </c>
+      <c r="C89" s="292"/>
+      <c r="D89" s="293">
+        <v>0</v>
+      </c>
+      <c r="E89" s="285"/>
+      <c r="F89" s="285">
+        <v>0</v>
+      </c>
+      <c r="G89" s="285"/>
+      <c r="H89" s="285">
+        <v>0</v>
+      </c>
+      <c r="I89" s="285"/>
+      <c r="J89" s="285">
+        <v>0</v>
+      </c>
+      <c r="K89" s="285"/>
+      <c r="L89" s="285">
+        <v>0</v>
+      </c>
+      <c r="M89" s="285"/>
+      <c r="N89" s="285">
+        <v>0</v>
+      </c>
+      <c r="O89" s="285"/>
+      <c r="P89" s="285">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="285"/>
+      <c r="R89" s="285">
+        <v>0</v>
+      </c>
+      <c r="S89" s="285"/>
+      <c r="T89" s="285">
+        <v>0</v>
+      </c>
+      <c r="U89" s="191"/>
     </row>
     <row r="90" spans="1:21" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A90" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B90" s="90">
-        <v>0</v>
-      </c>
-      <c r="C90" s="91"/>
-      <c r="D90" s="164">
-        <v>0</v>
-      </c>
-      <c r="E90" s="165"/>
-      <c r="F90" s="147">
-        <v>0</v>
-      </c>
-      <c r="G90" s="165"/>
-      <c r="H90" s="147">
-        <v>0</v>
-      </c>
-      <c r="I90" s="165"/>
-      <c r="J90" s="147">
-        <v>0</v>
-      </c>
-      <c r="K90" s="165"/>
-      <c r="L90" s="147">
-        <v>0</v>
-      </c>
-      <c r="M90" s="165"/>
-      <c r="N90" s="147">
-        <v>0</v>
-      </c>
-      <c r="O90" s="165"/>
-      <c r="P90" s="147">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="165"/>
-      <c r="R90" s="147">
-        <v>0</v>
-      </c>
-      <c r="S90" s="165"/>
-      <c r="T90" s="147">
-        <v>0</v>
-      </c>
-      <c r="U90" s="148"/>
+      <c r="B90" s="215">
+        <v>0</v>
+      </c>
+      <c r="C90" s="216"/>
+      <c r="D90" s="288">
+        <v>0</v>
+      </c>
+      <c r="E90" s="289"/>
+      <c r="F90" s="290">
+        <v>0</v>
+      </c>
+      <c r="G90" s="289"/>
+      <c r="H90" s="290">
+        <v>0</v>
+      </c>
+      <c r="I90" s="289"/>
+      <c r="J90" s="290">
+        <v>0</v>
+      </c>
+      <c r="K90" s="289"/>
+      <c r="L90" s="290">
+        <v>0</v>
+      </c>
+      <c r="M90" s="289"/>
+      <c r="N90" s="290">
+        <v>0</v>
+      </c>
+      <c r="O90" s="289"/>
+      <c r="P90" s="290">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="289"/>
+      <c r="R90" s="290">
+        <v>0</v>
+      </c>
+      <c r="S90" s="289"/>
+      <c r="T90" s="290">
+        <v>0</v>
+      </c>
+      <c r="U90" s="250"/>
     </row>
     <row r="91" spans="1:21" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="149" t="s">
+      <c r="A91" s="294" t="s">
         <v>31</v>
       </c>
-      <c r="B91" s="150"/>
-      <c r="C91" s="150"/>
-      <c r="D91" s="150"/>
-      <c r="E91" s="150"/>
-      <c r="F91" s="150"/>
-      <c r="G91" s="150"/>
-      <c r="H91" s="150"/>
-      <c r="I91" s="150"/>
-      <c r="J91" s="150"/>
-      <c r="K91" s="150"/>
-      <c r="L91" s="150"/>
-      <c r="M91" s="150"/>
-      <c r="N91" s="150"/>
-      <c r="O91" s="150"/>
-      <c r="P91" s="150"/>
-      <c r="Q91" s="150"/>
-      <c r="R91" s="150"/>
-      <c r="S91" s="150"/>
-      <c r="T91" s="150"/>
-      <c r="U91" s="151"/>
+      <c r="B91" s="295"/>
+      <c r="C91" s="295"/>
+      <c r="D91" s="295"/>
+      <c r="E91" s="295"/>
+      <c r="F91" s="295"/>
+      <c r="G91" s="295"/>
+      <c r="H91" s="295"/>
+      <c r="I91" s="295"/>
+      <c r="J91" s="295"/>
+      <c r="K91" s="295"/>
+      <c r="L91" s="295"/>
+      <c r="M91" s="295"/>
+      <c r="N91" s="295"/>
+      <c r="O91" s="295"/>
+      <c r="P91" s="295"/>
+      <c r="Q91" s="295"/>
+      <c r="R91" s="295"/>
+      <c r="S91" s="295"/>
+      <c r="T91" s="295"/>
+      <c r="U91" s="296"/>
     </row>
     <row r="92" spans="1:21" ht="10" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G92" s="28"/>
@@ -5920,264 +5923,264 @@
       <c r="T94" s="23"/>
     </row>
     <row r="95" spans="1:21" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="152" t="s">
+      <c r="A95" s="297" t="s">
         <v>28</v>
       </c>
-      <c r="B95" s="153"/>
-      <c r="C95" s="154" t="s">
+      <c r="B95" s="298"/>
+      <c r="C95" s="299" t="s">
         <v>27</v>
       </c>
-      <c r="D95" s="155"/>
-      <c r="E95" s="156" t="s">
+      <c r="D95" s="300"/>
+      <c r="E95" s="236" t="s">
         <v>26</v>
       </c>
-      <c r="F95" s="157"/>
-      <c r="G95" s="156" t="s">
+      <c r="F95" s="237"/>
+      <c r="G95" s="236" t="s">
         <v>25</v>
       </c>
-      <c r="H95" s="158"/>
-      <c r="I95" s="159" t="s">
+      <c r="H95" s="301"/>
+      <c r="I95" s="286" t="s">
         <v>24</v>
       </c>
-      <c r="J95" s="160"/>
-      <c r="K95" s="159" t="s">
+      <c r="J95" s="287"/>
+      <c r="K95" s="286" t="s">
         <v>23</v>
       </c>
-      <c r="L95" s="160"/>
-      <c r="M95" s="159" t="s">
+      <c r="L95" s="287"/>
+      <c r="M95" s="286" t="s">
         <v>22</v>
       </c>
-      <c r="N95" s="160"/>
-      <c r="O95" s="159" t="s">
+      <c r="N95" s="287"/>
+      <c r="O95" s="286" t="s">
         <v>21</v>
       </c>
-      <c r="P95" s="160"/>
-      <c r="Q95" s="159" t="s">
+      <c r="P95" s="287"/>
+      <c r="Q95" s="286" t="s">
         <v>20</v>
       </c>
-      <c r="R95" s="160"/>
-      <c r="S95" s="159" t="s">
+      <c r="R95" s="287"/>
+      <c r="S95" s="286" t="s">
         <v>19</v>
       </c>
-      <c r="T95" s="163"/>
+      <c r="T95" s="212"/>
     </row>
     <row r="96" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="140" t="s">
+      <c r="A96" s="302" t="s">
         <v>18</v>
       </c>
-      <c r="B96" s="141"/>
-      <c r="C96" s="142" t="s">
+      <c r="B96" s="303"/>
+      <c r="C96" s="306" t="s">
         <v>16</v>
       </c>
-      <c r="D96" s="143"/>
-      <c r="E96" s="144">
+      <c r="D96" s="307"/>
+      <c r="E96" s="308">
         <f>+SUM(G96:T96)</f>
         <v>0</v>
       </c>
-      <c r="F96" s="145"/>
-      <c r="G96" s="138"/>
-      <c r="H96" s="146"/>
-      <c r="I96" s="138"/>
-      <c r="J96" s="146"/>
-      <c r="K96" s="138"/>
-      <c r="L96" s="146"/>
-      <c r="M96" s="138"/>
-      <c r="N96" s="146"/>
-      <c r="O96" s="138"/>
-      <c r="P96" s="146"/>
-      <c r="Q96" s="138"/>
-      <c r="R96" s="146"/>
-      <c r="S96" s="138"/>
-      <c r="T96" s="139"/>
+      <c r="F96" s="309"/>
+      <c r="G96" s="310"/>
+      <c r="H96" s="311"/>
+      <c r="I96" s="310"/>
+      <c r="J96" s="311"/>
+      <c r="K96" s="310"/>
+      <c r="L96" s="311"/>
+      <c r="M96" s="310"/>
+      <c r="N96" s="311"/>
+      <c r="O96" s="310"/>
+      <c r="P96" s="311"/>
+      <c r="Q96" s="310"/>
+      <c r="R96" s="311"/>
+      <c r="S96" s="310"/>
+      <c r="T96" s="312"/>
     </row>
     <row r="97" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="132"/>
-      <c r="B97" s="133"/>
-      <c r="C97" s="136" t="s">
+      <c r="A97" s="304"/>
+      <c r="B97" s="305"/>
+      <c r="C97" s="313" t="s">
         <v>15</v>
       </c>
-      <c r="D97" s="137"/>
-      <c r="E97" s="120">
+      <c r="D97" s="314"/>
+      <c r="E97" s="315">
         <f>+SUM(G97:T97)</f>
         <v>0</v>
       </c>
-      <c r="F97" s="121"/>
-      <c r="G97" s="122"/>
-      <c r="H97" s="123"/>
-      <c r="I97" s="122"/>
-      <c r="J97" s="123"/>
-      <c r="K97" s="122"/>
-      <c r="L97" s="123"/>
-      <c r="M97" s="122"/>
-      <c r="N97" s="123"/>
-      <c r="O97" s="122"/>
-      <c r="P97" s="123"/>
-      <c r="Q97" s="122"/>
-      <c r="R97" s="123"/>
-      <c r="S97" s="122"/>
-      <c r="T97" s="129"/>
+      <c r="F97" s="316"/>
+      <c r="G97" s="317"/>
+      <c r="H97" s="318"/>
+      <c r="I97" s="317"/>
+      <c r="J97" s="318"/>
+      <c r="K97" s="317"/>
+      <c r="L97" s="318"/>
+      <c r="M97" s="317"/>
+      <c r="N97" s="318"/>
+      <c r="O97" s="317"/>
+      <c r="P97" s="318"/>
+      <c r="Q97" s="317"/>
+      <c r="R97" s="318"/>
+      <c r="S97" s="317"/>
+      <c r="T97" s="319"/>
     </row>
     <row r="98" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="132" t="s">
+      <c r="A98" s="304" t="s">
         <v>17</v>
       </c>
-      <c r="B98" s="133"/>
-      <c r="C98" s="136" t="s">
+      <c r="B98" s="305"/>
+      <c r="C98" s="313" t="s">
         <v>16</v>
       </c>
-      <c r="D98" s="137"/>
-      <c r="E98" s="120">
+      <c r="D98" s="314"/>
+      <c r="E98" s="315">
         <f>+SUM(G98:T98)</f>
         <v>0</v>
       </c>
-      <c r="F98" s="121"/>
-      <c r="G98" s="122"/>
-      <c r="H98" s="123"/>
-      <c r="I98" s="122"/>
-      <c r="J98" s="123"/>
-      <c r="K98" s="122"/>
-      <c r="L98" s="123"/>
-      <c r="M98" s="122"/>
-      <c r="N98" s="123"/>
-      <c r="O98" s="122"/>
-      <c r="P98" s="123"/>
-      <c r="Q98" s="122"/>
-      <c r="R98" s="123"/>
-      <c r="S98" s="122"/>
-      <c r="T98" s="129"/>
+      <c r="F98" s="316"/>
+      <c r="G98" s="317"/>
+      <c r="H98" s="318"/>
+      <c r="I98" s="317"/>
+      <c r="J98" s="318"/>
+      <c r="K98" s="317"/>
+      <c r="L98" s="318"/>
+      <c r="M98" s="317"/>
+      <c r="N98" s="318"/>
+      <c r="O98" s="317"/>
+      <c r="P98" s="318"/>
+      <c r="Q98" s="317"/>
+      <c r="R98" s="318"/>
+      <c r="S98" s="317"/>
+      <c r="T98" s="319"/>
     </row>
     <row r="99" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="134"/>
-      <c r="B99" s="135"/>
-      <c r="C99" s="130" t="s">
+      <c r="A99" s="320"/>
+      <c r="B99" s="321"/>
+      <c r="C99" s="322" t="s">
         <v>15</v>
       </c>
-      <c r="D99" s="131"/>
-      <c r="E99" s="120">
+      <c r="D99" s="323"/>
+      <c r="E99" s="315">
         <f>+SUM(G99:T99)</f>
         <v>0</v>
       </c>
-      <c r="F99" s="121"/>
-      <c r="G99" s="122"/>
-      <c r="H99" s="123"/>
-      <c r="I99" s="122"/>
-      <c r="J99" s="123"/>
-      <c r="K99" s="122"/>
-      <c r="L99" s="123"/>
-      <c r="M99" s="122"/>
-      <c r="N99" s="123"/>
-      <c r="O99" s="122"/>
-      <c r="P99" s="123"/>
-      <c r="Q99" s="122"/>
-      <c r="R99" s="123"/>
-      <c r="S99" s="122"/>
-      <c r="T99" s="129"/>
+      <c r="F99" s="316"/>
+      <c r="G99" s="317"/>
+      <c r="H99" s="318"/>
+      <c r="I99" s="317"/>
+      <c r="J99" s="318"/>
+      <c r="K99" s="317"/>
+      <c r="L99" s="318"/>
+      <c r="M99" s="317"/>
+      <c r="N99" s="318"/>
+      <c r="O99" s="317"/>
+      <c r="P99" s="318"/>
+      <c r="Q99" s="317"/>
+      <c r="R99" s="318"/>
+      <c r="S99" s="317"/>
+      <c r="T99" s="319"/>
     </row>
     <row r="100" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="116" t="s">
+      <c r="A100" s="324" t="s">
         <v>14</v>
       </c>
-      <c r="B100" s="117"/>
-      <c r="C100" s="118"/>
-      <c r="D100" s="119"/>
-      <c r="E100" s="120">
-        <v>0</v>
-      </c>
-      <c r="F100" s="121"/>
-      <c r="G100" s="122">
-        <v>0</v>
-      </c>
-      <c r="H100" s="123"/>
-      <c r="I100" s="122">
-        <v>0</v>
-      </c>
-      <c r="J100" s="123"/>
-      <c r="K100" s="122"/>
-      <c r="L100" s="123"/>
-      <c r="M100" s="122"/>
-      <c r="N100" s="123"/>
-      <c r="O100" s="122"/>
-      <c r="P100" s="123"/>
-      <c r="Q100" s="122"/>
-      <c r="R100" s="123"/>
-      <c r="S100" s="122"/>
-      <c r="T100" s="129"/>
+      <c r="B100" s="325"/>
+      <c r="C100" s="326"/>
+      <c r="D100" s="327"/>
+      <c r="E100" s="315">
+        <v>0</v>
+      </c>
+      <c r="F100" s="316"/>
+      <c r="G100" s="317">
+        <v>0</v>
+      </c>
+      <c r="H100" s="318"/>
+      <c r="I100" s="317">
+        <v>0</v>
+      </c>
+      <c r="J100" s="318"/>
+      <c r="K100" s="317"/>
+      <c r="L100" s="318"/>
+      <c r="M100" s="317"/>
+      <c r="N100" s="318"/>
+      <c r="O100" s="317"/>
+      <c r="P100" s="318"/>
+      <c r="Q100" s="317"/>
+      <c r="R100" s="318"/>
+      <c r="S100" s="317"/>
+      <c r="T100" s="319"/>
     </row>
     <row r="101" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="124" t="s">
+      <c r="A101" s="330" t="s">
         <v>13</v>
       </c>
-      <c r="B101" s="125"/>
-      <c r="C101" s="125"/>
-      <c r="D101" s="126"/>
-      <c r="E101" s="127">
-        <v>0</v>
-      </c>
-      <c r="F101" s="128"/>
-      <c r="G101" s="100"/>
-      <c r="H101" s="109"/>
-      <c r="I101" s="100">
-        <v>0</v>
-      </c>
-      <c r="J101" s="109"/>
-      <c r="K101" s="100"/>
-      <c r="L101" s="109"/>
-      <c r="M101" s="100">
-        <v>0</v>
-      </c>
-      <c r="N101" s="109"/>
-      <c r="O101" s="100"/>
-      <c r="P101" s="109"/>
-      <c r="Q101" s="100"/>
-      <c r="R101" s="109"/>
-      <c r="S101" s="100"/>
-      <c r="T101" s="101"/>
+      <c r="B101" s="331"/>
+      <c r="C101" s="331"/>
+      <c r="D101" s="332"/>
+      <c r="E101" s="333">
+        <v>0</v>
+      </c>
+      <c r="F101" s="334"/>
+      <c r="G101" s="335"/>
+      <c r="H101" s="336"/>
+      <c r="I101" s="335">
+        <v>0</v>
+      </c>
+      <c r="J101" s="336"/>
+      <c r="K101" s="335"/>
+      <c r="L101" s="336"/>
+      <c r="M101" s="335">
+        <v>0</v>
+      </c>
+      <c r="N101" s="336"/>
+      <c r="O101" s="335"/>
+      <c r="P101" s="336"/>
+      <c r="Q101" s="335"/>
+      <c r="R101" s="336"/>
+      <c r="S101" s="335"/>
+      <c r="T101" s="341"/>
     </row>
     <row r="102" spans="1:20" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="102" t="s">
+      <c r="A102" s="342" t="s">
         <v>12</v>
       </c>
-      <c r="B102" s="103"/>
-      <c r="C102" s="103"/>
-      <c r="D102" s="104"/>
-      <c r="E102" s="105">
+      <c r="B102" s="343"/>
+      <c r="C102" s="343"/>
+      <c r="D102" s="344"/>
+      <c r="E102" s="345">
         <f>SUM(E96:E101)</f>
         <v>0</v>
       </c>
-      <c r="F102" s="106"/>
-      <c r="G102" s="107">
+      <c r="F102" s="346"/>
+      <c r="G102" s="328">
         <f>+SUM(G96:H101)</f>
         <v>0</v>
       </c>
-      <c r="H102" s="108"/>
-      <c r="I102" s="107">
-        <v>0</v>
-      </c>
-      <c r="J102" s="108"/>
-      <c r="K102" s="107">
+      <c r="H102" s="329"/>
+      <c r="I102" s="328">
+        <v>0</v>
+      </c>
+      <c r="J102" s="329"/>
+      <c r="K102" s="328">
         <f>+SUM(K96:L101)</f>
         <v>0</v>
       </c>
-      <c r="L102" s="108"/>
-      <c r="M102" s="107">
-        <v>0</v>
-      </c>
-      <c r="N102" s="108"/>
-      <c r="O102" s="107">
+      <c r="L102" s="329"/>
+      <c r="M102" s="328">
+        <v>0</v>
+      </c>
+      <c r="N102" s="329"/>
+      <c r="O102" s="328">
         <f>+SUM(O97:P101)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="108"/>
-      <c r="Q102" s="107">
+      <c r="P102" s="329"/>
+      <c r="Q102" s="328">
         <f>+SUM(Q96:R101)</f>
         <v>0</v>
       </c>
-      <c r="R102" s="108"/>
-      <c r="S102" s="107">
+      <c r="R102" s="329"/>
+      <c r="S102" s="328">
         <f>+SUM(S96:T101)</f>
         <v>0</v>
       </c>
-      <c r="T102" s="108"/>
+      <c r="T102" s="329"/>
     </row>
     <row r="103" spans="1:20" ht="10" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="104" spans="1:20" ht="20" thickBot="1" x14ac:dyDescent="0.25">
@@ -6205,48 +6208,48 @@
       <c r="T104" s="18"/>
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A105" s="110"/>
-      <c r="B105" s="111"/>
-      <c r="C105" s="111"/>
-      <c r="D105" s="111"/>
-      <c r="E105" s="111"/>
-      <c r="F105" s="111"/>
-      <c r="G105" s="111"/>
-      <c r="H105" s="111"/>
-      <c r="I105" s="111"/>
-      <c r="J105" s="111"/>
-      <c r="K105" s="111"/>
-      <c r="L105" s="111"/>
-      <c r="M105" s="111"/>
-      <c r="N105" s="111"/>
-      <c r="O105" s="111"/>
-      <c r="P105" s="111"/>
-      <c r="Q105" s="111"/>
-      <c r="R105" s="111"/>
-      <c r="S105" s="111"/>
-      <c r="T105" s="112"/>
+      <c r="A105" s="347"/>
+      <c r="B105" s="348"/>
+      <c r="C105" s="348"/>
+      <c r="D105" s="348"/>
+      <c r="E105" s="348"/>
+      <c r="F105" s="348"/>
+      <c r="G105" s="348"/>
+      <c r="H105" s="348"/>
+      <c r="I105" s="348"/>
+      <c r="J105" s="348"/>
+      <c r="K105" s="348"/>
+      <c r="L105" s="348"/>
+      <c r="M105" s="348"/>
+      <c r="N105" s="348"/>
+      <c r="O105" s="348"/>
+      <c r="P105" s="348"/>
+      <c r="Q105" s="348"/>
+      <c r="R105" s="348"/>
+      <c r="S105" s="348"/>
+      <c r="T105" s="349"/>
     </row>
     <row r="106" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="113"/>
-      <c r="B106" s="114"/>
-      <c r="C106" s="114"/>
-      <c r="D106" s="114"/>
-      <c r="E106" s="114"/>
-      <c r="F106" s="114"/>
-      <c r="G106" s="114"/>
-      <c r="H106" s="114"/>
-      <c r="I106" s="114"/>
-      <c r="J106" s="114"/>
-      <c r="K106" s="114"/>
-      <c r="L106" s="114"/>
-      <c r="M106" s="114"/>
-      <c r="N106" s="114"/>
-      <c r="O106" s="114"/>
-      <c r="P106" s="114"/>
-      <c r="Q106" s="114"/>
-      <c r="R106" s="114"/>
-      <c r="S106" s="114"/>
-      <c r="T106" s="115"/>
+      <c r="A106" s="350"/>
+      <c r="B106" s="351"/>
+      <c r="C106" s="351"/>
+      <c r="D106" s="351"/>
+      <c r="E106" s="351"/>
+      <c r="F106" s="351"/>
+      <c r="G106" s="351"/>
+      <c r="H106" s="351"/>
+      <c r="I106" s="351"/>
+      <c r="J106" s="351"/>
+      <c r="K106" s="351"/>
+      <c r="L106" s="351"/>
+      <c r="M106" s="351"/>
+      <c r="N106" s="351"/>
+      <c r="O106" s="351"/>
+      <c r="P106" s="351"/>
+      <c r="Q106" s="351"/>
+      <c r="R106" s="351"/>
+      <c r="S106" s="351"/>
+      <c r="T106" s="352"/>
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A107" s="17"/>
@@ -6430,10 +6433,10 @@
     </row>
     <row r="116" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9"/>
-      <c r="B116" s="90">
-        <v>0</v>
-      </c>
-      <c r="C116" s="91"/>
+      <c r="B116" s="215">
+        <v>0</v>
+      </c>
+      <c r="C116" s="216"/>
       <c r="D116" s="8" t="s">
         <v>4</v>
       </c>
@@ -6451,10 +6454,10 @@
     </row>
     <row r="117" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A117" s="9"/>
-      <c r="B117" s="92">
-        <v>0</v>
-      </c>
-      <c r="C117" s="93"/>
+      <c r="B117" s="217">
+        <v>0</v>
+      </c>
+      <c r="C117" s="218"/>
       <c r="D117" s="8" t="s">
         <v>3</v>
       </c>
@@ -6472,10 +6475,10 @@
     </row>
     <row r="118" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9"/>
-      <c r="B118" s="94">
-        <v>0</v>
-      </c>
-      <c r="C118" s="95"/>
+      <c r="B118" s="194">
+        <v>0</v>
+      </c>
+      <c r="C118" s="195"/>
       <c r="D118" s="8" t="s">
         <v>2</v>
       </c>
@@ -6493,10 +6496,10 @@
     </row>
     <row r="119" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9"/>
-      <c r="B119" s="96">
-        <v>0</v>
-      </c>
-      <c r="C119" s="97"/>
+      <c r="B119" s="337">
+        <v>0</v>
+      </c>
+      <c r="C119" s="338"/>
       <c r="D119" s="8" t="s">
         <v>1</v>
       </c>
@@ -6514,10 +6517,10 @@
     </row>
     <row r="120" spans="1:15" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
-      <c r="B120" s="98">
-        <v>0</v>
-      </c>
-      <c r="C120" s="99"/>
+      <c r="B120" s="339">
+        <v>0</v>
+      </c>
+      <c r="C120" s="340"/>
       <c r="D120" s="4" t="s">
         <v>0</v>
       </c>
@@ -6535,29 +6538,402 @@
     </row>
   </sheetData>
   <mergeCells count="443">
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="S101:T101"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="G102:H102"/>
+    <mergeCell ref="I102:J102"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="O101:P101"/>
+    <mergeCell ref="Q101:R101"/>
+    <mergeCell ref="A105:T106"/>
+    <mergeCell ref="Q102:R102"/>
+    <mergeCell ref="S102:T102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="O102:P102"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="G101:H101"/>
+    <mergeCell ref="I101:J101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="O100:P100"/>
+    <mergeCell ref="Q100:R100"/>
+    <mergeCell ref="S100:T100"/>
+    <mergeCell ref="S98:T98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="G99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="Q99:R99"/>
+    <mergeCell ref="S99:T99"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="G100:H100"/>
+    <mergeCell ref="I100:J100"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="M100:N100"/>
+    <mergeCell ref="A98:B99"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="M98:N98"/>
+    <mergeCell ref="O98:P98"/>
+    <mergeCell ref="Q98:R98"/>
+    <mergeCell ref="S96:T96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="M97:N97"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="Q97:R97"/>
+    <mergeCell ref="S97:T97"/>
+    <mergeCell ref="A96:B97"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="G96:H96"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="M96:N96"/>
+    <mergeCell ref="O96:P96"/>
+    <mergeCell ref="Q96:R96"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="J90:K90"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="N90:O90"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="L89:M89"/>
+    <mergeCell ref="N89:O89"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="R89:S89"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="R87:S87"/>
+    <mergeCell ref="T89:U89"/>
+    <mergeCell ref="O95:P95"/>
+    <mergeCell ref="Q95:R95"/>
+    <mergeCell ref="S95:T95"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="R90:S90"/>
+    <mergeCell ref="T90:U90"/>
+    <mergeCell ref="A91:U91"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="M95:N95"/>
+    <mergeCell ref="T87:U87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="L88:M88"/>
+    <mergeCell ref="T88:U88"/>
+    <mergeCell ref="C82:D83"/>
+    <mergeCell ref="E82:F83"/>
+    <mergeCell ref="G82:H83"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="L87:M87"/>
+    <mergeCell ref="N88:O88"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="R88:S88"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="K79:M80"/>
+    <mergeCell ref="N79:O80"/>
+    <mergeCell ref="P79:Q80"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="G76:H76"/>
+    <mergeCell ref="L76:M77"/>
+    <mergeCell ref="N76:O77"/>
+    <mergeCell ref="P76:Q77"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="G77:H77"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="L75:M75"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="G74:H74"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="G75:H75"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="G71:H71"/>
+    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="N72:O72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="L71:M71"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="N65:O65"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="N67:O67"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="G68:H68"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="N63:O63"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="N64:O64"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="G61:H61"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="G62:H62"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="G55:H55"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="G56:H56"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="A38:S38"/>
+    <mergeCell ref="B48:B83"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="K48:K77"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="N51:O52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L65:M65"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="L51:M52"/>
+    <mergeCell ref="P51:Q52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="L49:M50"/>
+    <mergeCell ref="P49:Q50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="N49:O50"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="Q14:U14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="J25:K26"/>
+    <mergeCell ref="L25:M26"/>
+    <mergeCell ref="N25:O26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="Q15:U15"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="M19:U19"/>
+    <mergeCell ref="A18:U18"/>
+    <mergeCell ref="A16:U16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:U17"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:Q11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:U12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:U13"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A6:U6"/>
+    <mergeCell ref="A8:U8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="T10:U10"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="L27:M27"/>
@@ -6582,402 +6958,29 @@
     <mergeCell ref="C57:D57"/>
     <mergeCell ref="N28:O28"/>
     <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A6:U6"/>
-    <mergeCell ref="A8:U8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:Q11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:U12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:U13"/>
-    <mergeCell ref="Q15:U15"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="M19:U19"/>
-    <mergeCell ref="A18:U18"/>
-    <mergeCell ref="A16:U16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:U17"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="Q14:U14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="J25:K26"/>
-    <mergeCell ref="L25:M26"/>
-    <mergeCell ref="N25:O26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="L49:M50"/>
-    <mergeCell ref="P49:Q50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="N49:O50"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="L51:M52"/>
-    <mergeCell ref="P51:Q52"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="A38:S38"/>
-    <mergeCell ref="B48:B83"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="K48:K77"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="N51:O52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="G55:H55"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="G61:H61"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="G62:H62"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="N63:O63"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="G64:H64"/>
-    <mergeCell ref="N64:O64"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="N67:O67"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="G68:H68"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="G65:H65"/>
-    <mergeCell ref="N65:O65"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="G66:H66"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="N71:O71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="G72:H72"/>
-    <mergeCell ref="N72:O72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="L71:M71"/>
-    <mergeCell ref="L72:M72"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="G69:H69"/>
-    <mergeCell ref="N69:O69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="L69:M69"/>
-    <mergeCell ref="L70:M70"/>
-    <mergeCell ref="L75:M75"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="L73:M73"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="G76:H76"/>
-    <mergeCell ref="L76:M77"/>
-    <mergeCell ref="N76:O77"/>
-    <mergeCell ref="P76:Q77"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="G77:H77"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="K79:M80"/>
-    <mergeCell ref="N79:O80"/>
-    <mergeCell ref="P79:Q80"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="G81:H81"/>
-    <mergeCell ref="T87:U87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="L88:M88"/>
-    <mergeCell ref="T88:U88"/>
-    <mergeCell ref="C82:D83"/>
-    <mergeCell ref="E82:F83"/>
-    <mergeCell ref="G82:H83"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="L87:M87"/>
-    <mergeCell ref="N88:O88"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="R88:S88"/>
-    <mergeCell ref="N89:O89"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="R89:S89"/>
-    <mergeCell ref="N87:O87"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="R87:S87"/>
-    <mergeCell ref="T89:U89"/>
-    <mergeCell ref="O95:P95"/>
-    <mergeCell ref="Q95:R95"/>
-    <mergeCell ref="S95:T95"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="H90:I90"/>
-    <mergeCell ref="J90:K90"/>
-    <mergeCell ref="L90:M90"/>
-    <mergeCell ref="N90:O90"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="L89:M89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="R90:S90"/>
-    <mergeCell ref="T90:U90"/>
-    <mergeCell ref="A91:U91"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="M95:N95"/>
-    <mergeCell ref="A96:B97"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="G96:H96"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="K96:L96"/>
-    <mergeCell ref="M96:N96"/>
-    <mergeCell ref="O96:P96"/>
-    <mergeCell ref="Q96:R96"/>
-    <mergeCell ref="S96:T96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="M97:N97"/>
-    <mergeCell ref="O97:P97"/>
-    <mergeCell ref="Q97:R97"/>
-    <mergeCell ref="S97:T97"/>
-    <mergeCell ref="A98:B99"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="K98:L98"/>
-    <mergeCell ref="M98:N98"/>
-    <mergeCell ref="O98:P98"/>
-    <mergeCell ref="Q98:R98"/>
-    <mergeCell ref="Q100:R100"/>
-    <mergeCell ref="S100:T100"/>
-    <mergeCell ref="S98:T98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="G99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="K99:L99"/>
-    <mergeCell ref="M99:N99"/>
-    <mergeCell ref="O99:P99"/>
-    <mergeCell ref="Q99:R99"/>
-    <mergeCell ref="S99:T99"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="G100:H100"/>
-    <mergeCell ref="I100:J100"/>
-    <mergeCell ref="K100:L100"/>
-    <mergeCell ref="M100:N100"/>
-    <mergeCell ref="K102:L102"/>
-    <mergeCell ref="M102:N102"/>
-    <mergeCell ref="O102:P102"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="G101:H101"/>
-    <mergeCell ref="I101:J101"/>
-    <mergeCell ref="K101:L101"/>
-    <mergeCell ref="O100:P100"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="S101:T101"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="G102:H102"/>
-    <mergeCell ref="I102:J102"/>
-    <mergeCell ref="M101:N101"/>
-    <mergeCell ref="O101:P101"/>
-    <mergeCell ref="Q101:R101"/>
-    <mergeCell ref="A105:T106"/>
-    <mergeCell ref="Q102:R102"/>
-    <mergeCell ref="S102:T102"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C76:D76"/>
   </mergeCells>
   <conditionalFormatting sqref="A49:A81">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
